--- a/Versão5/VANT/Ontologia_DRONE.xlsx
+++ b/Versão5/VANT/Ontologia_DRONE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\VANT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9831A366-1EC3-4BDC-B2FD-D9A0DCF36860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8C59A2-3523-469E-B773-FEC6F1DCAEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="167">
   <si>
     <t>Edição</t>
   </si>
@@ -452,9 +452,6 @@
     <t>"É um voo de drone autônomo realizado sobre o CT da UFRJ"</t>
   </si>
   <si>
-    <t>"08/08/2024"</t>
-  </si>
-  <si>
     <t>formato.kml</t>
   </si>
   <si>
@@ -507,6 +504,75 @@
   </si>
   <si>
     <t>en</t>
+  </si>
+  <si>
+    <t>Contêiner</t>
+  </si>
+  <si>
+    <t>Informação</t>
+  </si>
+  <si>
+    <t>Definida</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
+  </si>
+  <si>
+    <t>Requerida</t>
+  </si>
+  <si>
+    <t>Manutençao_01</t>
+  </si>
+  <si>
+    <t>"Contêiner dos dados da Manutenção_01"</t>
+  </si>
+  <si>
+    <t>"09/08/2024"</t>
+  </si>
+  <si>
+    <t>Gestão</t>
+  </si>
+  <si>
+    <t>No.Projeto</t>
+  </si>
+  <si>
+    <t>Requisito.Espacial</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Mobiliário</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Equipamento</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
+  </si>
+  <si>
+    <t>Requisito.Sistemas</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información conforme al estándar NBR 19650-1. Definición del proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información conforme al estándar NBR 19650-1. Requisitos espaciales para el proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información conforme a la norma NBR 19650-1. Requisitos de mobiliario para el proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información conforme al estándar NBR 19650-1. Requisitos de Equipo para el Proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información conforme a la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</t>
   </si>
 </sst>
 </file>
@@ -690,26 +756,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6E896"/>
-        <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
     <fill>
@@ -728,6 +776,24 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE79D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
   </fills>
@@ -782,7 +848,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -852,16 +918,7 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -870,89 +927,122 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -982,6 +1072,84 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1068,6 +1236,14 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1385,12 +1561,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
+  <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.3046875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="56" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.4609375" style="48" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="9.15234375" style="13"/>
   </cols>
   <sheetData>
@@ -1401,8 +1578,8 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="54" t="s">
-        <v>141</v>
+      <c r="C1" s="46" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1412,8 +1589,8 @@
       <c r="B2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="55" t="s">
-        <v>142</v>
+      <c r="C2" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1423,8 +1600,8 @@
       <c r="B3" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C3" s="55" t="s">
-        <v>142</v>
+      <c r="C3" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1434,8 +1611,8 @@
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="55" t="s">
-        <v>142</v>
+      <c r="C4" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1446,8 +1623,8 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="55" t="s">
-        <v>142</v>
+      <c r="C5" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1458,8 +1635,8 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="55" t="s">
-        <v>142</v>
+      <c r="C6" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1469,19 +1646,19 @@
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="55" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="53" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="47" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="55" t="s">
-        <v>142</v>
+        <v>138</v>
+      </c>
+      <c r="C8" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1491,8 +1668,8 @@
       <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="55" t="s">
-        <v>142</v>
+      <c r="C9" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1502,8 +1679,8 @@
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="55" t="s">
-        <v>142</v>
+      <c r="C10" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1513,8 +1690,8 @@
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="55" t="s">
-        <v>142</v>
+      <c r="C11" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1524,8 +1701,8 @@
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="55" t="s">
-        <v>142</v>
+      <c r="C12" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1535,8 +1712,8 @@
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="55" t="s">
-        <v>142</v>
+      <c r="C13" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1546,8 +1723,8 @@
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="55" t="s">
-        <v>142</v>
+      <c r="C14" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1557,8 +1734,8 @@
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="55" t="s">
-        <v>142</v>
+      <c r="C15" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1568,8 +1745,8 @@
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="55" t="s">
-        <v>142</v>
+      <c r="C16" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1579,8 +1756,8 @@
       <c r="B17" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C17" s="55" t="s">
-        <v>142</v>
+      <c r="C17" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1589,10 +1766,10 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>45992.732927893521</v>
-      </c>
-      <c r="C18" s="55" t="s">
-        <v>142</v>
+        <v>46139.514405324073</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1602,8 +1779,8 @@
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="55" t="s">
-        <v>142</v>
+      <c r="C19" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1613,8 +1790,8 @@
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="55" t="s">
-        <v>142</v>
+      <c r="C20" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1624,8 +1801,8 @@
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="55" t="s">
-        <v>142</v>
+      <c r="C21" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1635,8 +1812,8 @@
       <c r="B22" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C22" s="55" t="s">
-        <v>142</v>
+      <c r="C22" s="47" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1647,20 +1824,20 @@
         <f>_xlfn.TRANSLATE(B22,"pt","es")</f>
         <v>Formalizar los datos de los vuelos de drones.</v>
       </c>
-      <c r="C23" s="55" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="53" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="45" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize data for drone flights.</v>
       </c>
-      <c r="C24" s="55" t="s">
-        <v>144</v>
+      <c r="C24" s="47" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1670,7 +1847,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
-  <dimension ref="A1:AA8"/>
+  <sheetPr codeName="Planilha2"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.84375" customWidth="1"/>
@@ -1684,754 +1862,1260 @@
     <col min="13" max="13" width="6.15234375" customWidth="1"/>
     <col min="14" max="14" width="5.53515625" customWidth="1"/>
     <col min="15" max="15" width="7.15234375" customWidth="1"/>
-    <col min="16" max="16" width="20.3046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.15234375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.3828125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="51.921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="3.69140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="3.84375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" customWidth="1"/>
-    <col min="26" max="26" width="5.15234375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.84375" customWidth="1"/>
+    <col min="21" max="21" width="6.07421875" customWidth="1"/>
+    <col min="22" max="22" width="8.69140625" style="59" customWidth="1"/>
+    <col min="23" max="23" width="6.3046875" style="62" customWidth="1"/>
+    <col min="24" max="24" width="6.15234375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.53515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3" style="58" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="39.61328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="29" t="s">
+      <c r="L1" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="29" t="s">
+      <c r="M1" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="29" t="s">
+      <c r="O1" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="P1" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="29" t="s">
+      <c r="Q1" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="R1" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="29" t="s">
+      <c r="S1" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="29" t="s">
+      <c r="T1" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="U1" s="29" t="s">
+      <c r="U1" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="V1" s="29" t="s">
+      <c r="V1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="31" t="s">
+      <c r="W1" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="X1" s="29" t="s">
+      <c r="X1" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y1" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="Y1" s="29" t="s">
+      <c r="Z1" s="57" t="s">
         <v>136</v>
       </c>
-      <c r="Z1" s="29" t="s">
+      <c r="AA1" s="43" t="s">
         <v>137</v>
       </c>
-      <c r="AA1" s="51" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="25">
+    </row>
+    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="49">
         <v>2</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="53" t="str">
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="M2" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N2" s="53" t="str">
+        <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
+        <v>Definida</v>
+      </c>
+      <c r="O2" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>No Projeto</v>
+      </c>
+      <c r="P2" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q2" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="R2" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="55" t="str">
+        <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
+        <v>Contêiner</v>
+      </c>
+      <c r="T2" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U2" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Definida</v>
+      </c>
+      <c r="V2" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W2" s="61" t="str">
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-UAS-",A2)</f>
+        <v>Key-UAS-2</v>
+      </c>
+      <c r="X2" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="44" t="str">
+        <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="49">
+        <v>3</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="G3" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M3" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N3" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O3" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Espacial</v>
+      </c>
+      <c r="P3" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q3" s="44" t="s">
+        <v>163</v>
+      </c>
+      <c r="R3" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T3" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U3" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V3" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W3" s="61" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-3</v>
+      </c>
+      <c r="X3" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="49">
+        <v>4</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="G4" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M4" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N4" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O4" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Mobiliário</v>
+      </c>
+      <c r="P4" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q4" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="R4" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T4" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U4" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V4" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W4" s="61" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-4</v>
+      </c>
+      <c r="X4" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="49">
+        <v>5</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M5" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N5" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O5" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Equipamento</v>
+      </c>
+      <c r="P5" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q5" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="R5" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T5" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U5" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V5" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W5" s="61" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-5</v>
+      </c>
+      <c r="X5" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="49">
+        <v>6</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="G6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="M6" s="53" t="str">
+        <f t="shared" si="0"/>
+        <v>Informação</v>
+      </c>
+      <c r="N6" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requerida</v>
+      </c>
+      <c r="O6" s="53" t="str">
+        <f t="shared" si="1"/>
+        <v>Requisito Sistemas</v>
+      </c>
+      <c r="P6" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q6" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="R6" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Contêiner</v>
+      </c>
+      <c r="T6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Informação</v>
+      </c>
+      <c r="U6" s="55" t="str">
+        <f t="shared" si="2"/>
+        <v>Requerida</v>
+      </c>
+      <c r="V6" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W6" s="61" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-6</v>
+      </c>
+      <c r="X6" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="49">
+        <v>7</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C7" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D7" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E7" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="F7" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="G2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="26" t="str">
-        <f t="shared" ref="L2:L3" si="0">_xlfn.CONCAT(SUBSTITUTE(C2,"1.",""))</f>
+      <c r="G7" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="56" t="str">
+        <f t="shared" ref="L7:L8" si="5">_xlfn.CONCAT(SUBSTITUTE(C7,"1.",""))</f>
         <v>Operação</v>
       </c>
-      <c r="M2" s="26" t="str">
-        <f t="shared" ref="M2:O7" si="1">_xlfn.CONCAT(SUBSTITUTE(D2,"."," "))</f>
+      <c r="M7" s="56" t="str">
+        <f t="shared" ref="M7:O12" si="6">_xlfn.CONCAT(SUBSTITUTE(D7,"."," "))</f>
         <v>Manutenção</v>
       </c>
-      <c r="N2" s="26" t="str">
-        <f t="shared" si="1"/>
+      <c r="N7" s="56" t="str">
+        <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O2" s="26" t="str">
-        <f t="shared" si="1"/>
+      <c r="O7" s="56" t="str">
+        <f t="shared" si="6"/>
         <v>Drone</v>
       </c>
-      <c r="P2" s="26" t="s">
+      <c r="P7" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="Q2" s="32" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","es")</f>
-        <v>Se trata de una aeronave tipo dron o UAS.</v>
-      </c>
-      <c r="R2" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="S2" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="T2" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="U2" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="V2" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="W2" s="33" t="str">
-        <f t="shared" ref="W2:W8" si="2">CONCATENATE("Key.",LEFT(C2,3),".",A2)</f>
-        <v>Key.Ope.2</v>
-      </c>
-      <c r="X2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z2" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="52" t="str">
-        <f>_xlfn.TRANSLATE(P2,"pt","en")</f>
+      <c r="Q7" s="44" t="str">
+        <f t="shared" ref="Q3:Q13" si="7">_xlfn.TRANSLATE(P7,"pt","es")</f>
+        <v>Es una aeronave tipo dron o UAS.</v>
+      </c>
+      <c r="R7" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="55" t="str">
+        <f t="shared" ref="S7:S13" si="8">SUBSTITUTE(C7, ".", " ")</f>
+        <v>Operação</v>
+      </c>
+      <c r="T7" s="55" t="str">
+        <f t="shared" ref="T7:T13" si="9">SUBSTITUTE(D7, ".", " ")</f>
+        <v>Manutenção</v>
+      </c>
+      <c r="U7" s="55" t="str">
+        <f t="shared" ref="U7:U13" si="10">SUBSTITUTE(E7, ".", " ")</f>
+        <v>Vistoria</v>
+      </c>
+      <c r="V7" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W7" s="61" t="str">
+        <f t="shared" ref="W7:W13" si="11">CONCATENATE("Key-UAS-",A7)</f>
+        <v>Key-UAS-7</v>
+      </c>
+      <c r="X7" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="44" t="str">
+        <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>It is a drone-type aircraft or UAS.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="25">
-        <v>3</v>
-      </c>
-      <c r="B3" s="18" t="s">
+    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="49">
+        <v>8</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C8" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D8" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E8" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F8" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="26" t="str">
-        <f t="shared" si="0"/>
-        <v>Operação</v>
-      </c>
-      <c r="M3" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Manutenção</v>
-      </c>
-      <c r="N3" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Vistoria</v>
-      </c>
-      <c r="O3" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Voo Plano</v>
-      </c>
-      <c r="P3" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q3" s="32" t="str">
-        <f>_xlfn.TRANSLATE(P3,"pt","es")</f>
-        <v>Plan de vuelo autónomo.</v>
-      </c>
-      <c r="R3" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="S3" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="T3" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="U3" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="V3" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="W3" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Key.Ope.3</v>
-      </c>
-      <c r="X3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="52" t="str">
-        <f t="shared" ref="AA3:AA8" si="3">_xlfn.TRANSLATE(P3,"pt","en")</f>
-        <v>Autonomous flight plan.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="25">
-        <v>4</v>
-      </c>
-      <c r="B4" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="26" t="str">
-        <f t="shared" ref="L4" si="4">_xlfn.CONCAT(SUBSTITUTE(C4,"1.",""))</f>
-        <v>Operação</v>
-      </c>
-      <c r="M4" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Manutenção</v>
-      </c>
-      <c r="N4" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Vistoria</v>
-      </c>
-      <c r="O4" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Voo Autônomo</v>
-      </c>
-      <c r="P4" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q4" s="32" t="str">
-        <f>_xlfn.TRANSLATE(P4,"pt","es")</f>
-        <v>Vuelo autónomo realizado con dron.</v>
-      </c>
-      <c r="R4" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="S4" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="T4" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="U4" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="V4" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="W4" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Key.Ope.4</v>
-      </c>
-      <c r="X4" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y4" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Autonomous flight carried out with a drone.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="25">
-        <v>5</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="G5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="26" t="str">
-        <f t="shared" ref="L5:L6" si="5">_xlfn.CONCAT(SUBSTITUTE(C5,"1.",""))</f>
-        <v>Operação</v>
-      </c>
-      <c r="M5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Manutenção</v>
-      </c>
-      <c r="N5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Vistoria</v>
-      </c>
-      <c r="O5" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Voo Manual</v>
-      </c>
-      <c r="P5" s="26" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q5" s="32" t="str">
-        <f t="shared" ref="Q5:Q7" si="6">_xlfn.TRANSLATE(P5,"pt","es")</f>
-        <v>Vuelo manual realizado con dron.</v>
-      </c>
-      <c r="R5" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="S5" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="T5" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="U5" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="V5" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="W5" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Key.Ope.5</v>
-      </c>
-      <c r="X5" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y5" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z5" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Manual flight carried out with drone.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="25">
-        <v>6</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="G6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="26" t="str">
+      <c r="G8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="56" t="str">
         <f t="shared" si="5"/>
         <v>Operação</v>
       </c>
-      <c r="M6" s="26" t="str">
-        <f t="shared" si="1"/>
+      <c r="M8" s="56" t="str">
+        <f t="shared" si="6"/>
         <v>Manutenção</v>
       </c>
-      <c r="N6" s="26" t="str">
-        <f t="shared" si="1"/>
+      <c r="N8" s="56" t="str">
+        <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O6" s="26" t="str">
-        <f t="shared" si="1"/>
+      <c r="O8" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Voo Plano</v>
+      </c>
+      <c r="P8" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q8" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v>Plan de vuelo autónomo.</v>
+      </c>
+      <c r="R8" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>Operação</v>
+      </c>
+      <c r="T8" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="U8" s="55" t="str">
+        <f t="shared" si="10"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="V8" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W8" s="61" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-UAS-8</v>
+      </c>
+      <c r="X8" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y8" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="44" t="str">
+        <f t="shared" ref="AA8:AA13" si="12">_xlfn.TRANSLATE(P8,"pt","en")</f>
+        <v>Autonomous flight plan.</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="49">
+        <v>9</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="56" t="str">
+        <f t="shared" ref="L9" si="13">_xlfn.CONCAT(SUBSTITUTE(C9,"1.",""))</f>
+        <v>Operação</v>
+      </c>
+      <c r="M9" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="N9" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="O9" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Voo Autônomo</v>
+      </c>
+      <c r="P9" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q9" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v>Vuelo autónomo realizado con un dron.</v>
+      </c>
+      <c r="R9" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>Operação</v>
+      </c>
+      <c r="T9" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="U9" s="55" t="str">
+        <f t="shared" si="10"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="V9" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W9" s="61" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-UAS-9</v>
+      </c>
+      <c r="X9" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y9" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v>Autonomous flight carried out with a drone.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="49">
+        <v>10</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="56" t="str">
+        <f t="shared" ref="L10:L11" si="14">_xlfn.CONCAT(SUBSTITUTE(C10,"1.",""))</f>
+        <v>Operação</v>
+      </c>
+      <c r="M10" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="N10" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="O10" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Voo Manual</v>
+      </c>
+      <c r="P10" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q10" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v>El vuelo manual se realiza con dron.</v>
+      </c>
+      <c r="R10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>Operação</v>
+      </c>
+      <c r="T10" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="U10" s="55" t="str">
+        <f t="shared" si="10"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="V10" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W10" s="61" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-UAS-10</v>
+      </c>
+      <c r="X10" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y10" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v>Manual flight carried out with drone.</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="49">
+        <v>11</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="56" t="str">
+        <f t="shared" si="14"/>
+        <v>Operação</v>
+      </c>
+      <c r="M11" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="N11" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="O11" s="56" t="str">
+        <f t="shared" si="6"/>
         <v>De Campo</v>
       </c>
-      <c r="P6" s="26" t="s">
+      <c r="P11" s="56" t="s">
         <v>87</v>
       </c>
-      <c r="Q6" s="32" t="str">
+      <c r="Q11" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v>Inspección realizada en el terreno.</v>
+      </c>
+      <c r="R11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>Operação</v>
+      </c>
+      <c r="T11" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="U11" s="55" t="str">
+        <f t="shared" si="10"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="V11" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W11" s="61" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-UAS-11</v>
+      </c>
+      <c r="X11" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y11" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v>Inspection carried out in the field.</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="49">
+        <v>12</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="56" t="str">
+        <f t="shared" ref="L12" si="15">_xlfn.CONCAT(SUBSTITUTE(C12,"1.",""))</f>
+        <v>Operação</v>
+      </c>
+      <c r="M12" s="56" t="str">
         <f t="shared" si="6"/>
-        <v>Inspección realizada en campo.</v>
-      </c>
-      <c r="R6" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="S6" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="T6" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="U6" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="V6" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="W6" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Key.Ope.6</v>
-      </c>
-      <c r="X6" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Inspection carried out in the field.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="25">
-        <v>7</v>
-      </c>
-      <c r="B7" s="18" t="s">
+        <v>Manutenção</v>
+      </c>
+      <c r="N12" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="O12" s="56" t="str">
+        <f t="shared" si="6"/>
+        <v>Banco Imagens</v>
+      </c>
+      <c r="P12" s="56" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q12" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v>Imágenes y vídeos de archivo de los vuelos.</v>
+      </c>
+      <c r="R12" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="55" t="str">
+        <f t="shared" si="8"/>
+        <v>Operação</v>
+      </c>
+      <c r="T12" s="55" t="str">
+        <f t="shared" si="9"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="U12" s="55" t="str">
+        <f t="shared" si="10"/>
+        <v>Vistoria</v>
+      </c>
+      <c r="V12" s="56" t="s">
+        <v>131</v>
+      </c>
+      <c r="W12" s="61" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-UAS-12</v>
+      </c>
+      <c r="X12" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="44" t="str">
+        <f t="shared" si="12"/>
+        <v>Stock images and videos of the flights.</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="49">
+        <v>13</v>
+      </c>
+      <c r="B13" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="26" t="str">
-        <f t="shared" ref="L7" si="7">_xlfn.CONCAT(SUBSTITUTE(C7,"1.",""))</f>
-        <v>Operação</v>
-      </c>
-      <c r="M7" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Manutenção</v>
-      </c>
-      <c r="N7" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Vistoria</v>
-      </c>
-      <c r="O7" s="26" t="str">
-        <f t="shared" si="1"/>
-        <v>Banco Imagens</v>
-      </c>
-      <c r="P7" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q7" s="32" t="str">
-        <f t="shared" si="6"/>
-        <v>Imágenes y videos de archivo de los vuelos.</v>
-      </c>
-      <c r="R7" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="S7" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="T7" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="U7" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="V7" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="W7" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Key.Ope.7</v>
-      </c>
-      <c r="X7" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y7" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="52" t="str">
-        <f t="shared" si="3"/>
-        <v>Stock images and videos of the flights.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="25">
-        <v>8</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="48" t="s">
+      <c r="C13" s="41" t="s">
+        <v>127</v>
+      </c>
+      <c r="D13" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="E13" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="F13" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="G13" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="56" t="str">
+        <f t="shared" ref="L13" si="16">_xlfn.CONCAT(SUBSTITUTE(C13,"1.",""))</f>
+        <v>Temporal</v>
+      </c>
+      <c r="M13" s="56" t="str">
+        <f t="shared" ref="M13" si="17">_xlfn.CONCAT(SUBSTITUTE(D13,"."," "))</f>
+        <v>Evento</v>
+      </c>
+      <c r="N13" s="56" t="str">
+        <f t="shared" ref="N13" si="18">_xlfn.CONCAT(SUBSTITUTE(E13,"."," "))</f>
+        <v>Calendário</v>
+      </c>
+      <c r="O13" s="56" t="str">
+        <f t="shared" ref="O13" si="19">_xlfn.CONCAT(SUBSTITUTE(F13,"."," "))</f>
+        <v>Data</v>
+      </c>
+      <c r="P13" s="56" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="26" t="str">
-        <f t="shared" ref="L8" si="8">_xlfn.CONCAT(SUBSTITUTE(C8,"1.",""))</f>
+      <c r="Q13" s="44" t="str">
+        <f t="shared" si="7"/>
+        <v>Fecha del evento de inspección.</v>
+      </c>
+      <c r="R13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="55" t="str">
+        <f t="shared" si="8"/>
         <v>Temporal</v>
       </c>
-      <c r="M8" s="26" t="str">
-        <f t="shared" ref="M8" si="9">_xlfn.CONCAT(SUBSTITUTE(D8,"."," "))</f>
+      <c r="T13" s="55" t="str">
+        <f t="shared" si="9"/>
         <v>Evento</v>
       </c>
-      <c r="N8" s="26" t="str">
-        <f t="shared" ref="N8" si="10">_xlfn.CONCAT(SUBSTITUTE(E8,"."," "))</f>
+      <c r="U13" s="55" t="str">
+        <f t="shared" si="10"/>
         <v>Calendário</v>
       </c>
-      <c r="O8" s="26" t="str">
-        <f t="shared" ref="O8" si="11">_xlfn.CONCAT(SUBSTITUTE(F8,"."," "))</f>
-        <v>Data</v>
-      </c>
-      <c r="P8" s="26" t="s">
+      <c r="V13" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="Q8" s="32" t="str">
-        <f t="shared" ref="Q8" si="12">_xlfn.TRANSLATE(P8,"pt","es")</f>
-        <v>Fecha del evento de inspección.</v>
-      </c>
-      <c r="R8" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="S8" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="T8" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="U8" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="V8" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="W8" s="33" t="str">
-        <f t="shared" si="2"/>
-        <v>Key.Tem.8</v>
-      </c>
-      <c r="X8" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y8" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z8" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="52" t="str">
-        <f t="shared" si="3"/>
+      <c r="W13" s="61" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-UAS-13</v>
+      </c>
+      <c r="X13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y13" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z13" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="44" t="str">
+        <f t="shared" si="12"/>
         <v>Date of the inspection event.</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="11" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F5">
-    <cfRule type="duplicateValues" dxfId="6" priority="153"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F1048576 F1:F5">
-    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA7:AA13">
+    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA8">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="F7:F10 F1">
+    <cfRule type="duplicateValues" dxfId="20" priority="165"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F1048576 F1 F7:F10">
+    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:O1">
+    <cfRule type="cellIs" dxfId="13" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -2442,6 +3126,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
+  <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
   <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2587,6 +3272,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
+  <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2615,13 +3301,13 @@
       <c r="A2" s="7">
         <v>2</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="38" t="s">
+      <c r="B2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="31" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2632,11 +3318,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
+  <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.3046875" customWidth="1"/>
+    <col min="2" max="2" width="8.23046875" customWidth="1"/>
     <col min="3" max="3" width="7.15234375" customWidth="1"/>
     <col min="4" max="4" width="3.3828125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.3828125" bestFit="1" customWidth="1"/>
@@ -2672,37 +3359,37 @@
       <c r="C1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="39" t="s">
+      <c r="I1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="39" t="s">
+      <c r="J1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="39" t="s">
+      <c r="M1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="43" t="s">
+      <c r="N1" s="36" t="s">
         <v>31</v>
       </c>
       <c r="O1" s="15" t="s">
@@ -2729,13 +3416,13 @@
       <c r="V1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="43" t="s">
+      <c r="W1" s="36" t="s">
         <v>2</v>
       </c>
       <c r="X1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="43" t="s">
+      <c r="Y1" s="36" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2744,72 +3431,72 @@
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E2" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>100</v>
-      </c>
-      <c r="E2" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="R2" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="42" t="s">
+      <c r="T2" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V2" s="42" t="s">
+      <c r="V2" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="42" t="s">
+      <c r="X2" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y2" s="20" t="s">
@@ -2821,72 +3508,72 @@
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C3" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="E3" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="F3" s="42" t="s">
+      <c r="E3" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="H3" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R3" s="42" t="s">
+      <c r="H3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="R3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="42" t="s">
+      <c r="T3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="42" t="s">
+      <c r="V3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X3" s="42" t="s">
+      <c r="X3" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y3" s="20" t="s">
@@ -2903,67 +3590,67 @@
       <c r="C4" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="35" t="s">
         <v>92</v>
       </c>
       <c r="E4" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="H4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" s="42" t="s">
+      <c r="H4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T4" s="42" t="s">
+      <c r="T4" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V4" s="42" t="s">
+      <c r="V4" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X4" s="42" t="s">
+      <c r="X4" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y4" s="20" t="s">
@@ -2980,67 +3667,67 @@
       <c r="C5" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="40" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H5" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="42" t="s">
+      <c r="H5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K5" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="L5" s="42" t="s">
+      <c r="L5" s="35" t="s">
         <v>9</v>
       </c>
       <c r="M5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N5" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P5" s="42" t="s">
+      <c r="N5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P5" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Q5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="42" t="s">
+      <c r="R5" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T5" s="42" t="s">
+      <c r="T5" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V5" s="42" t="s">
+      <c r="V5" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W5" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X5" s="42" t="s">
+      <c r="X5" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y5" s="20" t="s">
@@ -3057,67 +3744,67 @@
       <c r="C6" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="47" t="s">
+      <c r="E6" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="H6" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="42" t="s">
+      <c r="H6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K6" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="L6" s="42" t="s">
+      <c r="L6" s="35" t="s">
         <v>9</v>
       </c>
       <c r="M6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N6" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="42" t="s">
+      <c r="N6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Q6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R6" s="42" t="s">
+      <c r="R6" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T6" s="42" t="s">
+      <c r="T6" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V6" s="42" t="s">
+      <c r="V6" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X6" s="42" t="s">
+      <c r="X6" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y6" s="20" t="s">
@@ -3134,67 +3821,67 @@
       <c r="C7" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="40" t="s">
+      <c r="D7" s="33" t="s">
         <v>102</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K7" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="L7" s="42" t="s">
+      <c r="L7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="M7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N7" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P7" s="42" t="s">
+      <c r="N7" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Q7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R7" s="42" t="s">
+      <c r="R7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T7" s="42" t="s">
+      <c r="T7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V7" s="42" t="s">
+      <c r="V7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X7" s="42" t="s">
+      <c r="X7" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y7" s="20" t="s">
@@ -3211,67 +3898,67 @@
       <c r="C8" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="D8" s="33" t="s">
         <v>102</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="L8" s="42" t="s">
+      <c r="L8" s="35" t="s">
         <v>9</v>
       </c>
       <c r="M8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="42" t="s">
+      <c r="N8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Q8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R8" s="42" t="s">
+      <c r="R8" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T8" s="42" t="s">
+      <c r="T8" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V8" s="42" t="s">
+      <c r="V8" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X8" s="42" t="s">
+      <c r="X8" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y8" s="20" t="s">
@@ -3288,67 +3975,67 @@
       <c r="C9" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="D9" s="33" t="s">
         <v>102</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="40" t="s">
+      <c r="F9" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="J9" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="L9" s="42" t="s">
-        <v>127</v>
+      <c r="L9" s="35" t="s">
+        <v>126</v>
       </c>
       <c r="M9" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="N9" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="O9" s="41" t="s">
+      <c r="N9" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="O9" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="P9" s="42" t="s">
+      <c r="P9" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Q9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R9" s="42" t="s">
+      <c r="R9" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T9" s="42" t="s">
+      <c r="T9" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V9" s="42" t="s">
+      <c r="V9" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X9" s="42" t="s">
+      <c r="X9" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y9" s="20" t="s">
@@ -3365,67 +4052,67 @@
       <c r="C10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="D10" s="33" t="s">
         <v>102</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="34" t="s">
         <v>110</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="42" t="s">
+      <c r="J10" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="L10" s="42" t="s">
-        <v>127</v>
+      <c r="L10" s="35" t="s">
+        <v>126</v>
       </c>
       <c r="M10" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="O10" s="41" t="s">
+      <c r="N10" s="33" t="s">
+        <v>132</v>
+      </c>
+      <c r="O10" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="P10" s="42" t="s">
+      <c r="P10" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Q10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="R10" s="42" t="s">
+      <c r="R10" s="35" t="s">
         <v>9</v>
       </c>
       <c r="S10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="42" t="s">
+      <c r="T10" s="35" t="s">
         <v>9</v>
       </c>
       <c r="U10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V10" s="42" t="s">
+      <c r="V10" s="35" t="s">
         <v>9</v>
       </c>
       <c r="W10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X10" s="42" t="s">
+      <c r="X10" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y10" s="20" t="s">
@@ -3435,11 +4122,16 @@
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
   <conditionalFormatting sqref="B1:B10">
-    <cfRule type="duplicateValues" dxfId="2" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="144"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/VANT/Ontologia_DRONE.xlsx
+++ b/Versão5/VANT/Ontologia_DRONE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\VANT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB8C59A2-3523-469E-B773-FEC6F1DCAEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AD7233-0108-442A-ABBB-EF4B9D36EDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="169">
   <si>
     <t>Edição</t>
   </si>
@@ -377,9 +377,6 @@
     <t>data</t>
   </si>
   <si>
-    <t>"É data de voo de vistoria"</t>
-  </si>
-  <si>
     <t>é.drone</t>
   </si>
   <si>
@@ -573,6 +570,15 @@
   </si>
   <si>
     <t>Define un contenedor de información conforme a la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</t>
+  </si>
+  <si>
+    <t>Manutençao_02</t>
+  </si>
+  <si>
+    <t>"30/03/2026"</t>
+  </si>
+  <si>
+    <t>"É data de um voo de vistoria"</t>
   </si>
 </sst>
 </file>
@@ -848,7 +854,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1020,7 +1026,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1034,55 +1039,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1156,16 +1113,48 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1579,7 +1568,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1590,7 +1579,7 @@
         <v>80</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1598,10 +1587,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1612,7 +1601,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1624,7 +1613,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1636,7 +1625,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1647,7 +1636,7 @@
         <v>32</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -1655,10 +1644,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1669,7 +1658,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1680,7 +1669,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1691,7 +1680,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1702,7 +1691,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1713,7 +1702,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1724,7 +1713,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1735,7 +1724,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1746,7 +1735,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1754,10 +1743,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1766,10 +1755,10 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46139.514405324073</v>
+        <v>46139.537489699076</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1780,7 +1769,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1791,7 +1780,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1802,7 +1791,7 @@
         <v>12</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1810,10 +1799,10 @@
         <v>33</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -1825,19 +1814,19 @@
         <v>Formalizar los datos de los vuelos de drones.</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="45" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize data for drone flights.</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -1856,7 +1845,7 @@
     <col min="3" max="3" width="5.3046875" customWidth="1"/>
     <col min="4" max="4" width="5.84375" customWidth="1"/>
     <col min="5" max="5" width="4.69140625" customWidth="1"/>
-    <col min="6" max="6" width="6.53515625" customWidth="1"/>
+    <col min="6" max="6" width="9.3046875" customWidth="1"/>
     <col min="7" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.15234375" customWidth="1"/>
@@ -1868,8 +1857,8 @@
     <col min="19" max="19" width="4.3828125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="5.84375" customWidth="1"/>
     <col min="21" max="21" width="6.07421875" customWidth="1"/>
-    <col min="22" max="22" width="8.69140625" style="59" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" style="62" customWidth="1"/>
+    <col min="22" max="22" width="8.69140625" customWidth="1"/>
+    <col min="23" max="23" width="6.3046875" style="61" customWidth="1"/>
     <col min="24" max="24" width="6.15234375" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="4.53515625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="3" style="58" bestFit="1" customWidth="1"/>
@@ -1943,20 +1932,20 @@
       <c r="V1" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="W1" s="60" t="s">
+      <c r="W1" s="59" t="s">
         <v>59</v>
       </c>
       <c r="X1" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y1" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="Y1" s="26" t="s">
+      <c r="Z1" s="57" t="s">
         <v>135</v>
       </c>
-      <c r="Z1" s="57" t="s">
+      <c r="AA1" s="43" t="s">
         <v>136</v>
-      </c>
-      <c r="AA1" s="43" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -1964,19 +1953,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="51" t="s">
         <v>152</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="50" t="s">
-        <v>145</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>153</v>
       </c>
       <c r="G2" s="52" t="s">
         <v>9</v>
@@ -2010,10 +1999,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="R2" s="54" t="s">
         <v>9</v>
@@ -2031,9 +2020,9 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W2" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W2" s="60" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-UAS-",A2)</f>
         <v>Key-UAS-2</v>
       </c>
@@ -2056,19 +2045,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C3" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>145</v>
-      </c>
       <c r="E3" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G3" s="52" t="s">
         <v>9</v>
@@ -2102,10 +2091,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="R3" s="54" t="s">
         <v>9</v>
@@ -2123,9 +2112,9 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W3" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W3" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-3</v>
       </c>
@@ -2148,19 +2137,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="50" t="s">
-        <v>145</v>
-      </c>
       <c r="E4" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F4" s="51" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G4" s="52" t="s">
         <v>9</v>
@@ -2194,10 +2183,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="44" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R4" s="54" t="s">
         <v>9</v>
@@ -2215,9 +2204,9 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W4" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W4" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-4</v>
       </c>
@@ -2240,19 +2229,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C5" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="50" t="s">
-        <v>145</v>
-      </c>
       <c r="E5" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G5" s="52" t="s">
         <v>9</v>
@@ -2286,10 +2275,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="44" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="R5" s="54" t="s">
         <v>9</v>
@@ -2307,9 +2296,9 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W5" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W5" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-5</v>
       </c>
@@ -2332,19 +2321,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C6" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="D6" s="50" t="s">
-        <v>145</v>
-      </c>
       <c r="E6" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G6" s="52" t="s">
         <v>9</v>
@@ -2378,10 +2367,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R6" s="54" t="s">
         <v>9</v>
@@ -2399,9 +2388,9 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W6" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W6" s="60" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-6</v>
       </c>
@@ -2473,7 +2462,7 @@
         <v>89</v>
       </c>
       <c r="Q7" s="44" t="str">
-        <f t="shared" ref="Q3:Q13" si="7">_xlfn.TRANSLATE(P7,"pt","es")</f>
+        <f t="shared" ref="Q7:Q13" si="7">_xlfn.TRANSLATE(P7,"pt","es")</f>
         <v>Es una aeronave tipo dron o UAS.</v>
       </c>
       <c r="R7" s="54" t="s">
@@ -2492,9 +2481,9 @@
         <v>Vistoria</v>
       </c>
       <c r="V7" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W7" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W7" s="60" t="str">
         <f t="shared" ref="W7:W13" si="11">CONCATENATE("Key-UAS-",A7)</f>
         <v>Key-UAS-7</v>
       </c>
@@ -2529,7 +2518,7 @@
         <v>81</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" s="52" t="s">
         <v>9</v>
@@ -2563,7 +2552,7 @@
         <v>Voo Plano</v>
       </c>
       <c r="P8" s="56" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q8" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2585,9 +2574,9 @@
         <v>Vistoria</v>
       </c>
       <c r="V8" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W8" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W8" s="60" t="str">
         <f t="shared" si="11"/>
         <v>Key-UAS-8</v>
       </c>
@@ -2678,9 +2667,9 @@
         <v>Vistoria</v>
       </c>
       <c r="V9" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W9" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W9" s="60" t="str">
         <f t="shared" si="11"/>
         <v>Key-UAS-9</v>
       </c>
@@ -2771,9 +2760,9 @@
         <v>Vistoria</v>
       </c>
       <c r="V10" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W10" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W10" s="60" t="str">
         <f t="shared" si="11"/>
         <v>Key-UAS-10</v>
       </c>
@@ -2864,9 +2853,9 @@
         <v>Vistoria</v>
       </c>
       <c r="V11" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W11" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W11" s="60" t="str">
         <f t="shared" si="11"/>
         <v>Key-UAS-11</v>
       </c>
@@ -2901,7 +2890,7 @@
         <v>81</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G12" s="52" t="s">
         <v>9</v>
@@ -2935,7 +2924,7 @@
         <v>Banco Imagens</v>
       </c>
       <c r="P12" s="56" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q12" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2957,9 +2946,9 @@
         <v>Vistoria</v>
       </c>
       <c r="V12" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W12" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W12" s="60" t="str">
         <f t="shared" si="11"/>
         <v>Key-UAS-12</v>
       </c>
@@ -2985,13 +2974,13 @@
         <v>78</v>
       </c>
       <c r="C13" s="41" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="41" t="s">
         <v>127</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="E13" s="42" t="s">
         <v>128</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>129</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>97</v>
@@ -3028,7 +3017,7 @@
         <v>Data</v>
       </c>
       <c r="P13" s="56" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q13" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3050,9 +3039,9 @@
         <v>Calendário</v>
       </c>
       <c r="V13" s="56" t="s">
-        <v>131</v>
-      </c>
-      <c r="W13" s="61" t="str">
+        <v>130</v>
+      </c>
+      <c r="W13" s="60" t="str">
         <f t="shared" si="11"/>
         <v>Key-UAS-13</v>
       </c>
@@ -3071,51 +3060,39 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AA7:AA13">
-    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
+  <conditionalFormatting sqref="A2:A13">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F7:F10 F1">
-    <cfRule type="duplicateValues" dxfId="20" priority="165"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F1048576 F1 F7:F10">
-    <cfRule type="duplicateValues" dxfId="14" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="13" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
+  <conditionalFormatting sqref="AA1:AA13">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A13">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
@@ -3319,7 +3296,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:Y10"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.69140625" bestFit="1" customWidth="1"/>
@@ -3431,10 +3408,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D2" s="33" t="s">
         <v>99</v>
@@ -3446,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H2" s="37" t="s">
         <v>9</v>
@@ -3508,22 +3485,22 @@
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="E3" s="39" t="s">
-        <v>151</v>
+        <v>152</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>108</v>
       </c>
       <c r="F3" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>101</v>
+        <v>149</v>
       </c>
       <c r="H3" s="37" t="s">
         <v>9</v>
@@ -3585,22 +3562,22 @@
         <v>4</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>106</v>
+        <v>97</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>150</v>
       </c>
       <c r="F4" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="20" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="H4" s="37" t="s">
         <v>9</v>
@@ -3662,22 +3639,22 @@
         <v>5</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="40" t="s">
-        <v>119</v>
+        <v>100</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>167</v>
       </c>
       <c r="F5" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="H5" s="37" t="s">
         <v>9</v>
@@ -3685,16 +3662,16 @@
       <c r="I5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="L5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="20" t="s">
+      <c r="J5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="38" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="37" t="s">
@@ -3703,10 +3680,10 @@
       <c r="O5" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q5" s="20" t="s">
+      <c r="P5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="38" t="s">
         <v>9</v>
       </c>
       <c r="R5" s="35" t="s">
@@ -3739,22 +3716,22 @@
         <v>6</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="40" t="s">
-        <v>120</v>
+        <v>88</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>105</v>
       </c>
       <c r="F6" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H6" s="37" t="s">
         <v>9</v>
@@ -3762,16 +3739,16 @@
       <c r="I6" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="L6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="20" t="s">
+      <c r="J6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="38" t="s">
         <v>9</v>
       </c>
       <c r="N6" s="37" t="s">
@@ -3780,10 +3757,10 @@
       <c r="O6" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="20" t="s">
+      <c r="P6" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q6" s="38" t="s">
         <v>9</v>
       </c>
       <c r="R6" s="35" t="s">
@@ -3816,22 +3793,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>93</v>
+        <v>115</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>118</v>
       </c>
       <c r="F7" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H7" s="37" t="s">
         <v>9</v>
@@ -3843,7 +3820,7 @@
         <v>16</v>
       </c>
       <c r="K7" s="20" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="L7" s="35" t="s">
         <v>9</v>
@@ -3893,22 +3870,22 @@
         <v>8</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>93</v>
+        <v>115</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>119</v>
       </c>
       <c r="F8" s="35" t="s">
         <v>16</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="H8" s="37" t="s">
         <v>9</v>
@@ -3920,7 +3897,7 @@
         <v>16</v>
       </c>
       <c r="K8" s="20" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="L8" s="35" t="s">
         <v>9</v>
@@ -3970,46 +3947,46 @@
         <v>9</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="I9" s="34" t="s">
-        <v>98</v>
+      <c r="F9" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>9</v>
       </c>
       <c r="J9" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="L9" s="35" t="s">
-        <v>126</v>
+        <v>9</v>
       </c>
       <c r="M9" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="N9" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="O9" s="34" t="s">
-        <v>115</v>
+        <v>9</v>
+      </c>
+      <c r="N9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="38" t="s">
+        <v>9</v>
       </c>
       <c r="P9" s="35" t="s">
         <v>9</v>
@@ -4047,91 +4024,245 @@
         <v>10</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E10" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F10" s="33" t="s">
-        <v>108</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="34" t="s">
-        <v>109</v>
+      <c r="F10" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>9</v>
       </c>
       <c r="J10" s="35" t="s">
         <v>16</v>
       </c>
       <c r="K10" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="R10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="W10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y10" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="16">
+        <v>11</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="I11" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="J11" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L11" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="L10" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="M10" s="20" t="s">
+      <c r="M11" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="33" t="s">
-        <v>132</v>
-      </c>
-      <c r="O10" s="34" t="s">
+      <c r="N11" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="O11" s="34" t="s">
         <v>114</v>
       </c>
-      <c r="P10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="W10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y10" s="20" t="s">
+      <c r="P11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="R11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U11" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="W11" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y11" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="16">
+        <v>12</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="I12" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="L12" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="O12" s="34" t="s">
+        <v>113</v>
+      </c>
+      <c r="P12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="R12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="W12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="20" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B10">
-    <cfRule type="duplicateValues" dxfId="6" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="169"/>
+  <conditionalFormatting sqref="B1:B12">
+    <cfRule type="duplicateValues" dxfId="5" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="169"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="144"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/VANT/Ontologia_DRONE.xlsx
+++ b/Versão5/VANT/Ontologia_DRONE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\VANT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84AD7233-0108-442A-ABBB-EF4B9D36EDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C3C517-8C1A-4EF3-BDAF-8123DA018FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="178">
   <si>
     <t>Edição</t>
   </si>
@@ -133,10 +133,6 @@
   </si>
   <si>
     <t>N°</t>
-  </si>
-  <si>
-    <t>Fato
-(14)</t>
   </si>
   <si>
     <t>https://github.com/JLMenegotto/RepoOnto#</t>
@@ -362,9 +358,6 @@
     <t>Voo2</t>
   </si>
   <si>
-    <t>"É um voo de drone autônomo"</t>
-  </si>
-  <si>
     <t>Data</t>
   </si>
   <si>
@@ -380,9 +373,6 @@
     <t>é.drone</t>
   </si>
   <si>
-    <t>Plano01</t>
-  </si>
-  <si>
     <t>Voo.Plano</t>
   </si>
   <si>
@@ -392,18 +382,9 @@
     <t>"Mavic 2 Pro"</t>
   </si>
   <si>
-    <t>"É aparelho de drone modelo Mavic"</t>
-  </si>
-  <si>
-    <t>é.voo.realizado</t>
-  </si>
-  <si>
     <t>Data02</t>
   </si>
   <si>
-    <t>Plano02</t>
-  </si>
-  <si>
     <t>Drones</t>
   </si>
   <si>
@@ -428,12 +409,6 @@
     <t>url</t>
   </si>
   <si>
-    <t>"http://ufrj//ct//vistorias//predio//banco01"</t>
-  </si>
-  <si>
-    <t>"http://ufrj//ct//vistorias//predio//banco02"</t>
-  </si>
-  <si>
     <t>"É o banco de imagens de voo de manutenção predial"</t>
   </si>
   <si>
@@ -443,15 +418,9 @@
     <t>"VG_CT_Principal_2024_CT_Eixos_E1_E1_2024_08_08_08_14.kml"</t>
   </si>
   <si>
-    <t>"É um voo de drone autônomo sobre o CT da UFRJ"</t>
-  </si>
-  <si>
     <t>"É um voo de drone autônomo realizado sobre o CT da UFRJ"</t>
   </si>
   <si>
-    <t>formato.kml</t>
-  </si>
-  <si>
     <t>Temporal</t>
   </si>
   <si>
@@ -470,9 +439,6 @@
     <t>é.pertencente.a</t>
   </si>
   <si>
-    <t>"É um plano de voo planejado para o drone Mavic 2"</t>
-  </si>
-  <si>
     <t>CategoriaRvt</t>
   </si>
   <si>
@@ -579,13 +545,73 @@
   </si>
   <si>
     <t>"É data de um voo de vistoria"</t>
+  </si>
+  <si>
+    <t>arquivo.kml</t>
+  </si>
+  <si>
+    <t>"Contêiner dos dados da Manutenção do Predio 01"</t>
+  </si>
+  <si>
+    <t>Ope_Predio_01</t>
+  </si>
+  <si>
+    <t>"http://ufrj//ct//vistorias//predio//"</t>
+  </si>
+  <si>
+    <t>"banco01"</t>
+  </si>
+  <si>
+    <t>"banco02"</t>
+  </si>
+  <si>
+    <t>Plano_A</t>
+  </si>
+  <si>
+    <t>Plano_B</t>
+  </si>
+  <si>
+    <t>é.realizado.com</t>
+  </si>
+  <si>
+    <t>é.plano.de.voo</t>
+  </si>
+  <si>
+    <t>"É um plano de voo de drone autônomo sobre o CT da UFRJ"</t>
+  </si>
+  <si>
+    <t>"É aparelho de drone modelo Mavic 2"</t>
+  </si>
+  <si>
+    <t>Val</t>
+  </si>
+  <si>
+    <t>categoria.revit</t>
+  </si>
+  <si>
+    <t>classe.ifc</t>
+  </si>
+  <si>
+    <t>código.abnt</t>
+  </si>
+  <si>
+    <t>"[ 2Q.18.18 ]"</t>
+  </si>
+  <si>
+    <t>"[ - ]"</t>
+  </si>
+  <si>
+    <t>"[ OST_Entourage ]"</t>
+  </si>
+  <si>
+    <t>"[ IfcVehicle ]"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -667,6 +693,12 @@
       <color theme="1"/>
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="23">
@@ -854,7 +886,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1034,12 +1066,178 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1568,7 +1766,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="46" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1576,10 +1774,10 @@
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C2" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1587,10 +1785,10 @@
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C3" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1601,7 +1799,7 @@
         <v>19</v>
       </c>
       <c r="C4" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1613,7 +1811,7 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1625,7 +1823,7 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1633,10 +1831,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -1644,10 +1842,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="C8" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1658,7 +1856,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1669,7 +1867,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1680,7 +1878,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1691,7 +1889,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1702,7 +1900,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1713,7 +1911,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1724,7 +1922,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1735,7 +1933,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1743,10 +1941,10 @@
         <v>10</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C17" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1755,10 +1953,10 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46139.537489699076</v>
+        <v>46214.401976620371</v>
       </c>
       <c r="C18" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1769,7 +1967,7 @@
         <v>12</v>
       </c>
       <c r="C19" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1780,7 +1978,7 @@
         <v>12</v>
       </c>
       <c r="C20" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
@@ -1791,42 +1989,42 @@
         <v>12</v>
       </c>
       <c r="C21" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C22" s="47" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="6" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","es")</f>
         <v>Formalizar los datos de los vuelos de drones.</v>
       </c>
       <c r="C23" s="47" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:3" s="45" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize data for drone flights.</v>
       </c>
       <c r="C24" s="47" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1867,85 +2065,85 @@
   <sheetData>
     <row r="1" spans="1:27" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="P1" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q1" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="S1" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="29" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="F1" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="G1" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="H1" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="I1" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="J1" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="K1" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>72</v>
-      </c>
-      <c r="O1" s="26" t="s">
-        <v>73</v>
-      </c>
-      <c r="P1" s="26" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q1" s="26" t="s">
-        <v>75</v>
-      </c>
-      <c r="R1" s="27" t="s">
+      <c r="T1" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="26" t="s">
+      <c r="U1" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="V1" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="T1" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="U1" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="V1" s="27" t="s">
-        <v>37</v>
-      </c>
       <c r="W1" s="59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X1" s="26" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="Y1" s="26" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="Z1" s="57" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="AA1" s="43" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
@@ -1953,19 +2151,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E2" s="50" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="G2" s="52" t="s">
         <v>9</v>
@@ -1999,10 +2197,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="44" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="Q2" s="44" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="R2" s="54" t="s">
         <v>9</v>
@@ -2020,7 +2218,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W2" s="60" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-UAS-",A2)</f>
@@ -2045,19 +2243,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="G3" s="52" t="s">
         <v>9</v>
@@ -2091,10 +2289,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="44" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="Q3" s="44" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="R3" s="54" t="s">
         <v>9</v>
@@ -2112,7 +2310,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W3" s="60" t="str">
         <f t="shared" si="3"/>
@@ -2137,19 +2335,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C4" s="51" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D4" s="50" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="51" t="s">
         <v>144</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>155</v>
       </c>
       <c r="G4" s="52" t="s">
         <v>9</v>
@@ -2183,10 +2381,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="44" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="Q4" s="44" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="R4" s="54" t="s">
         <v>9</v>
@@ -2204,7 +2402,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W4" s="60" t="str">
         <f t="shared" si="3"/>
@@ -2229,19 +2427,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C5" s="51" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D5" s="50" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E5" s="50" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F5" s="51" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="G5" s="52" t="s">
         <v>9</v>
@@ -2275,10 +2473,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="44" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="Q5" s="44" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="R5" s="54" t="s">
         <v>9</v>
@@ -2296,7 +2494,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W5" s="60" t="str">
         <f t="shared" si="3"/>
@@ -2321,19 +2519,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D6" s="50" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E6" s="50" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F6" s="51" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="G6" s="52" t="s">
         <v>9</v>
@@ -2367,10 +2565,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="44" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="Q6" s="44" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="R6" s="54" t="s">
         <v>9</v>
@@ -2388,7 +2586,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W6" s="60" t="str">
         <f t="shared" si="3"/>
@@ -2413,19 +2611,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G7" s="52" t="s">
         <v>9</v>
@@ -2459,7 +2657,7 @@
         <v>Drone</v>
       </c>
       <c r="P7" s="56" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q7" s="44" t="str">
         <f t="shared" ref="Q7:Q13" si="7">_xlfn.TRANSLATE(P7,"pt","es")</f>
@@ -2481,7 +2679,7 @@
         <v>Vistoria</v>
       </c>
       <c r="V7" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W7" s="60" t="str">
         <f t="shared" ref="W7:W13" si="11">CONCATENATE("Key-UAS-",A7)</f>
@@ -2506,19 +2704,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G8" s="52" t="s">
         <v>9</v>
@@ -2552,7 +2750,7 @@
         <v>Voo Plano</v>
       </c>
       <c r="P8" s="56" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q8" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2574,7 +2772,7 @@
         <v>Vistoria</v>
       </c>
       <c r="V8" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W8" s="60" t="str">
         <f t="shared" si="11"/>
@@ -2599,19 +2797,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C9" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>83</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>84</v>
       </c>
       <c r="G9" s="52" t="s">
         <v>9</v>
@@ -2645,7 +2843,7 @@
         <v>Voo Autônomo</v>
       </c>
       <c r="P9" s="56" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q9" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2667,7 +2865,7 @@
         <v>Vistoria</v>
       </c>
       <c r="V9" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W9" s="60" t="str">
         <f t="shared" si="11"/>
@@ -2692,19 +2890,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" s="52" t="s">
         <v>9</v>
@@ -2738,7 +2936,7 @@
         <v>Voo Manual</v>
       </c>
       <c r="P10" s="56" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q10" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2760,7 +2958,7 @@
         <v>Vistoria</v>
       </c>
       <c r="V10" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W10" s="60" t="str">
         <f t="shared" si="11"/>
@@ -2785,19 +2983,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G11" s="52" t="s">
         <v>9</v>
@@ -2831,7 +3029,7 @@
         <v>De Campo</v>
       </c>
       <c r="P11" s="56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q11" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2853,7 +3051,7 @@
         <v>Vistoria</v>
       </c>
       <c r="V11" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W11" s="60" t="str">
         <f t="shared" si="11"/>
@@ -2878,19 +3076,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="G12" s="52" t="s">
         <v>9</v>
@@ -2924,7 +3122,7 @@
         <v>Banco Imagens</v>
       </c>
       <c r="P12" s="56" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="Q12" s="44" t="str">
         <f t="shared" si="7"/>
@@ -2946,7 +3144,7 @@
         <v>Vistoria</v>
       </c>
       <c r="V12" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W12" s="60" t="str">
         <f t="shared" si="11"/>
@@ -2971,19 +3169,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C13" s="41" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="D13" s="41" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G13" s="52" t="s">
         <v>9</v>
@@ -3017,7 +3215,7 @@
         <v>Data</v>
       </c>
       <c r="P13" s="56" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="Q13" s="44" t="str">
         <f t="shared" si="7"/>
@@ -3039,7 +3237,7 @@
         <v>Calendário</v>
       </c>
       <c r="V13" s="56" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="W13" s="60" t="str">
         <f t="shared" si="11"/>
@@ -3061,36 +3259,36 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A13">
-    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F10 F1">
-    <cfRule type="duplicateValues" dxfId="9" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14:F1048576 F1 F7:F10">
-    <cfRule type="duplicateValues" dxfId="8" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="7" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA13">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3117,64 +3315,64 @@
         <v>1</v>
       </c>
       <c r="B1" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="E1" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="F1" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="G1" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="H1" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="I1" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="J1" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="22" t="s">
+      <c r="K1" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="22" t="s">
+      <c r="L1" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="M1" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="M1" s="22" t="s">
+      <c r="N1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="N1" s="22" t="s">
+      <c r="O1" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="O1" s="22" t="s">
+      <c r="P1" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="P1" s="22" t="s">
+      <c r="Q1" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" s="22" t="s">
+      <c r="R1" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="R1" s="22" t="s">
+      <c r="S1" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="S1" s="22" t="s">
+      <c r="T1" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="T1" s="22" t="s">
+      <c r="U1" s="22" t="s">
         <v>57</v>
-      </c>
-      <c r="U1" s="22" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
@@ -3268,10 +3466,10 @@
         <v>14</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3296,37 +3494,39 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:AA62"/>
   <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="1.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.23046875" customWidth="1"/>
+    <col min="2" max="2" width="6.53515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.15234375" customWidth="1"/>
-    <col min="4" max="4" width="3.3828125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.15234375" customWidth="1"/>
-    <col min="7" max="7" width="22.84375" customWidth="1"/>
-    <col min="8" max="8" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.15234375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.3046875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.53515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.15234375" customWidth="1"/>
-    <col min="15" max="15" width="7.3046875" customWidth="1"/>
-    <col min="16" max="16" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.3046875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.765625" customWidth="1"/>
+    <col min="6" max="6" width="6.3046875" customWidth="1"/>
+    <col min="7" max="7" width="4.23046875" customWidth="1"/>
+    <col min="8" max="8" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.4609375" customWidth="1"/>
+    <col min="10" max="10" width="2.69140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.07421875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2.3828125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.3046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.3046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="25.23046875" customWidth="1"/>
+    <col min="18" max="18" width="4.84375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27.53515625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="2.84375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="2.84375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.84375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.69140625" style="66" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.3828125" style="66" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="3.84375" style="66" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.15234375" style="66" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="5.3046875" style="66"/>
+    <col min="27" max="27" width="5.921875" style="66" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -3348,10 +3548,10 @@
       <c r="G1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="32" t="s">
+      <c r="H1" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="15" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="32" t="s">
@@ -3360,28 +3560,28 @@
       <c r="K1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="M1" s="32" t="s">
+      <c r="M1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="36" t="s">
-        <v>31</v>
+      <c r="N1" s="15" t="s">
+        <v>15</v>
       </c>
       <c r="O1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="15" t="s">
+      <c r="P1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="15" t="s">
+      <c r="Q1" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="32" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="15" t="s">
@@ -3390,147 +3590,159 @@
       <c r="U1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="V1" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="36" t="s">
-        <v>2</v>
-      </c>
-      <c r="X1" s="15" t="s">
+      <c r="W1" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="X1" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="36" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Y1" s="63" t="s">
+        <v>170</v>
+      </c>
+      <c r="Z1" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA1" s="63" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="16">
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M2" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="N2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="H2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="R2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="35" t="s">
+      <c r="Q2" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="R2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="65" t="s">
         <v>9</v>
       </c>
       <c r="W2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="35" t="s">
+      <c r="X2" s="37" t="s">
         <v>9</v>
       </c>
       <c r="Y2" s="20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z2" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA2" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="16">
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M3" s="40" t="s">
+        <v>162</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="H3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q3" s="38" t="s">
-        <v>9</v>
+      <c r="Q3" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="R3" s="35" t="s">
         <v>9</v>
@@ -3544,70 +3756,76 @@
       <c r="U3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="35" t="s">
+      <c r="V3" s="65" t="s">
         <v>9</v>
       </c>
       <c r="W3" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X3" s="35" t="s">
+      <c r="X3" s="37" t="s">
         <v>9</v>
       </c>
       <c r="Y3" s="20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z3" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="16">
         <v>4</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="F4" s="35" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="M4" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="N4" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="M4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="38" t="s">
-        <v>9</v>
+      <c r="Q4" s="20" t="s">
+        <v>112</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>9</v>
@@ -3621,147 +3839,159 @@
       <c r="U4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V4" s="35" t="s">
+      <c r="V4" s="65" t="s">
         <v>9</v>
       </c>
       <c r="W4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X4" s="35" t="s">
+      <c r="X4" s="37" t="s">
         <v>9</v>
       </c>
       <c r="Y4" s="20" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="Z4" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="20" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="16">
         <v>5</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>167</v>
-      </c>
-      <c r="F5" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N5" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="P5" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="H5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="R5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U5" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="W5" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X5" s="35" t="s">
-        <v>9</v>
+      <c r="Q5" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="R5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="U5" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="V5" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="W5" s="67" t="s">
+        <v>176</v>
+      </c>
+      <c r="X5" s="37" t="s">
+        <v>172</v>
       </c>
       <c r="Y5" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>177</v>
+      </c>
+      <c r="Z5" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA5" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="16">
         <v>6</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>93</v>
+        <v>164</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F6" s="35" t="s">
+      <c r="F6" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q6" s="38" t="s">
-        <v>9</v>
+      <c r="Q6" s="20" t="s">
+        <v>168</v>
       </c>
       <c r="R6" s="35" t="s">
         <v>9</v>
@@ -3775,70 +4005,76 @@
       <c r="U6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V6" s="35" t="s">
-        <v>9</v>
+      <c r="V6" s="65" t="s">
+        <v>171</v>
       </c>
       <c r="W6" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X6" s="35" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="X6" s="37" t="s">
+        <v>172</v>
       </c>
       <c r="Y6" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+      <c r="Z6" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA6" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="16">
         <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="E7" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P7" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="L7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P7" s="35" t="s">
-        <v>9</v>
-      </c>
       <c r="Q7" s="20" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>9</v>
@@ -3852,417 +4088,646 @@
       <c r="U7" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V7" s="35" t="s">
-        <v>9</v>
+      <c r="V7" s="65" t="s">
+        <v>171</v>
       </c>
       <c r="W7" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X7" s="35" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="X7" s="37" t="s">
+        <v>172</v>
       </c>
       <c r="Y7" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+      <c r="Z7" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA7" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="16">
         <v>8</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>117</v>
-      </c>
-      <c r="E8" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="35" t="s">
+        <v>141</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="35" t="s">
+      <c r="Q8" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="R8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="V8" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="W8" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="X8" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y8" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z8" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA8" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="16">
+        <v>9</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="K8" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="L8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="W8" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X8" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y8" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="16">
-        <v>9</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="L9" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" s="35" t="s">
-        <v>9</v>
-      </c>
       <c r="Q9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T9" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V9" s="35" t="s">
-        <v>9</v>
+        <v>138</v>
+      </c>
+      <c r="R9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="U9" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="V9" s="65" t="s">
+        <v>171</v>
       </c>
       <c r="W9" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X9" s="35" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="X9" s="37" t="s">
+        <v>172</v>
       </c>
       <c r="Y9" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+      <c r="Z9" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA9" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="16">
         <v>10</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>121</v>
+      </c>
+      <c r="I10" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P10" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="L10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P10" s="35" t="s">
-        <v>9</v>
-      </c>
       <c r="Q10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V10" s="35" t="s">
-        <v>9</v>
+        <v>157</v>
+      </c>
+      <c r="R10" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="U10" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="V10" s="65" t="s">
+        <v>171</v>
       </c>
       <c r="W10" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X10" s="35" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="X10" s="37" t="s">
+        <v>172</v>
       </c>
       <c r="Y10" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+      <c r="Z10" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA10" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="16">
         <v>11</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>93</v>
+        <v>9</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>9</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>102</v>
+        <v>9</v>
       </c>
       <c r="H11" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O11" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P11" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="R11" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="L11" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="M11" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="N11" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="O11" s="34" t="s">
-        <v>114</v>
-      </c>
-      <c r="P11" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q11" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T11" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U11" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V11" s="35" t="s">
-        <v>9</v>
+      <c r="U11" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="V11" s="65" t="s">
+        <v>171</v>
       </c>
       <c r="W11" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X11" s="35" t="s">
-        <v>9</v>
+        <v>175</v>
+      </c>
+      <c r="X11" s="37" t="s">
+        <v>172</v>
       </c>
       <c r="Y11" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>175</v>
+      </c>
+      <c r="Z11" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA11" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="16">
         <v>12</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>109</v>
+        <v>167</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>164</v>
       </c>
       <c r="H12" s="33" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="I12" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="J12" s="35" t="s">
+      <c r="J12" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P12" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="L12" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="M12" s="20" t="s">
+      <c r="Q12" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="R12" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="S12" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="T12" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V12" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="W12" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="X12" s="37" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y12" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z12" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA12" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="16">
+        <v>13</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="N12" s="33" t="s">
-        <v>131</v>
-      </c>
-      <c r="O12" s="34" t="s">
+      <c r="I13" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="K13" s="34" t="s">
+        <v>103</v>
+      </c>
+      <c r="L13" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P13" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="R13" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="S13" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="P12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="W12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y12" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
+      <c r="T13" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V13" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="W13" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="X13" s="65" t="s">
+        <v>172</v>
+      </c>
+      <c r="Y13" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="Z13" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AA13" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14"/>
+      <c r="AA14"/>
+    </row>
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15"/>
+      <c r="AA15"/>
+    </row>
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16"/>
+      <c r="AA16"/>
+    </row>
+    <row r="17" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="18" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="20" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="21" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="22" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="23" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="24" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="25" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="26" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="28" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="31" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="35" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="37" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="42" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="56" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B12">
-    <cfRule type="duplicateValues" dxfId="5" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="169"/>
+  <conditionalFormatting sqref="B1:B13">
+    <cfRule type="duplicateValues" dxfId="21" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="230"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="178"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  <conditionalFormatting sqref="E8:E9">
+    <cfRule type="duplicateValues" dxfId="18" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12">
+    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I8">
+    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9">
+    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V63:AA1048576 V1:AA4 V5 X5 Z5:AA5 X7:X12 V7:W13 V6:AA6 Y7:AA13">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X13">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W5">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y5">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/VANT/Ontologia_DRONE.xlsx
+++ b/Versão5/VANT/Ontologia_DRONE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\VANT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C3C517-8C1A-4EF3-BDAF-8123DA018FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3EC93E9-172E-449F-BEA9-4A6C012A6392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="173">
   <si>
     <t>Edição</t>
   </si>
@@ -304,9 +304,6 @@
     <t>Especie</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
     <t>Equivalente a</t>
   </si>
   <si>
@@ -475,15 +472,9 @@
     <t>Informação</t>
   </si>
   <si>
-    <t>Definida</t>
-  </si>
-  <si>
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
   </si>
   <si>
-    <t>Requerida</t>
-  </si>
-  <si>
     <t>Manutençao_01</t>
   </si>
   <si>
@@ -496,9 +487,6 @@
     <t>Gestão</t>
   </si>
   <si>
-    <t>No.Projeto</t>
-  </si>
-  <si>
     <t>Requisito.Espacial</t>
   </si>
   <si>
@@ -523,21 +511,6 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Define un contenedor de información conforme al estándar NBR 19650-1. Definición del proyecto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información conforme al estándar NBR 19650-1. Requisitos espaciales para el proyecto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información conforme a la norma NBR 19650-1. Requisitos de mobiliario para el proyecto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información conforme al estándar NBR 19650-1. Requisitos de Equipo para el Proyecto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información conforme a la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</t>
-  </si>
-  <si>
     <t>Manutençao_02</t>
   </si>
   <si>
@@ -605,6 +578,18 @@
   </si>
   <si>
     <t>"[ IfcVehicle ]"</t>
+  </si>
+  <si>
+    <t>Conceito</t>
+  </si>
+  <si>
+    <t>Contêineres</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
+  </si>
+  <si>
+    <t>[ 5I ]</t>
   </si>
 </sst>
 </file>
@@ -818,12 +803,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFBE79D"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFFFC7CE"/>
       </patternFill>
@@ -832,6 +811,12 @@
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor rgb="FFD9F2D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE389"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -886,7 +871,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -962,15 +947,9 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1004,12 +983,6 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1028,96 +1001,65 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="2" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="60">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1240,6 +1182,34 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1300,22 +1270,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1426,11 +1380,253 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="2" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1750,59 +1946,59 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1124724F-B8C4-4B86-9028-743FC73CDDB0}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.3828125" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.3046875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="3.4609375" style="48" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="13"/>
+    <col min="1" max="1" width="10.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" style="13" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" s="10" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="46" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C1" s="42" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>78</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>103</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C4" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1810,11 +2006,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1822,188 +2018,188 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" s="45" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C7" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" s="41" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C8" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46214.401976620371</v>
-      </c>
-      <c r="C18" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+        <v>46216.40917071759</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C22" s="47" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+      <c r="C22" s="43" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>33</v>
       </c>
@@ -2011,20 +2207,20 @@
         <f>_xlfn.TRANSLATE(B22,"pt","es")</f>
         <v>Formalizar los datos de los vuelos de drones.</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" s="45" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="C23" s="43" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" s="41" customFormat="1" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B24" s="6" t="str">
         <f>_xlfn.TRANSLATE(B22,"pt","en")</f>
         <v>Formalize data for drone flights.</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>131</v>
+      <c r="C24" s="43" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2036,65 +2232,65 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA13"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.84375" customWidth="1"/>
-    <col min="2" max="2" width="4.3046875" customWidth="1"/>
-    <col min="3" max="3" width="5.3046875" customWidth="1"/>
-    <col min="4" max="4" width="5.84375" customWidth="1"/>
-    <col min="5" max="5" width="4.69140625" customWidth="1"/>
-    <col min="6" max="6" width="9.3046875" customWidth="1"/>
-    <col min="7" max="11" width="6.3828125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.15234375" customWidth="1"/>
-    <col min="14" max="14" width="5.53515625" customWidth="1"/>
-    <col min="15" max="15" width="7.15234375" customWidth="1"/>
-    <col min="16" max="16" width="47.3828125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="51.921875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="3.69140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.3828125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.84375" customWidth="1"/>
-    <col min="21" max="21" width="6.07421875" customWidth="1"/>
-    <col min="22" max="22" width="8.69140625" customWidth="1"/>
-    <col min="23" max="23" width="6.3046875" style="61" customWidth="1"/>
-    <col min="24" max="24" width="6.15234375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.53515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3" style="58" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="39.61328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.28515625" style="48" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="40.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6" style="48" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6" style="48" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="48" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="67.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="40.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="57" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="57" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="29" t="s">
+      <c r="F1" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="27" t="s">
         <v>68</v>
       </c>
       <c r="L1" s="26" t="s">
@@ -2115,7 +2311,7 @@
       <c r="Q1" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="R1" s="26" t="s">
         <v>75</v>
       </c>
       <c r="S1" s="26" t="s">
@@ -2127,1168 +2323,1173 @@
       <c r="U1" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="V1" s="27" t="s">
+      <c r="V1" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="W1" s="59" t="s">
+      <c r="W1" s="46" t="s">
         <v>58</v>
       </c>
       <c r="X1" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y1" s="26" t="s">
         <v>122</v>
       </c>
-      <c r="Y1" s="26" t="s">
+      <c r="Z1" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="Z1" s="57" t="s">
+      <c r="AA1" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="AA1" s="43" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="49">
+    </row>
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="55">
         <v>2</v>
       </c>
-      <c r="B2" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="51" t="s">
+      <c r="B2" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>134</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>141</v>
-      </c>
-      <c r="G2" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="53" t="str">
+      <c r="E2" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2" s="60" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="45" t="str">
         <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="M2" s="53" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M2" s="45" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N2" s="53" t="str">
+      <c r="N2" s="45" t="str">
         <f t="shared" ref="N2:O6" si="1">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E2),"."," ")," De "," de "))</f>
-        <v>Definida</v>
-      </c>
-      <c r="O2" s="53" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O2" s="45" t="str">
         <f t="shared" si="1"/>
-        <v>No Projeto</v>
-      </c>
-      <c r="P2" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q2" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="R2" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="55" t="str">
+        <v>Contêiner</v>
+      </c>
+      <c r="P2" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q2" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="R2" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="40" t="str">
         <f t="shared" ref="S2:U6" si="2">SUBSTITUTE(C2, ".", " ")</f>
-        <v>Contêiner</v>
-      </c>
-      <c r="T2" s="55" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T2" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U2" s="55" t="str">
+      <c r="U2" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Definida</v>
-      </c>
-      <c r="V2" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W2" s="60" t="str">
-        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key-UAS-",A2)</f>
+        <v>Contêineres</v>
+      </c>
+      <c r="V2" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W2" s="47" t="str">
+        <f t="shared" ref="W2:W13" si="3">CONCATENATE("Key-UAS-",A2)</f>
         <v>Key-UAS-2</v>
       </c>
-      <c r="X2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z2" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA2" s="44" t="str">
+      <c r="X2" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y2" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="40" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA2" s="40" t="str">
         <f t="shared" ref="AA2:AA6" si="4">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="49">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="55">
         <v>3</v>
       </c>
-      <c r="B3" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="C3" s="51" t="s">
+      <c r="B3" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E3" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" s="51" t="s">
-        <v>142</v>
-      </c>
-      <c r="G3" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="53" t="str">
+      <c r="E3" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="60" t="s">
+        <v>138</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="45" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M3" s="53" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M3" s="45" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N3" s="53" t="str">
+      <c r="N3" s="45" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O3" s="53" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O3" s="45" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Espacial</v>
       </c>
-      <c r="P3" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q3" s="44" t="s">
-        <v>151</v>
-      </c>
-      <c r="R3" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="55" t="str">
+      <c r="P3" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q3" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="R3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T3" s="55" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T3" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U3" s="55" t="str">
+      <c r="U3" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V3" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W3" s="60" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V3" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W3" s="47" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-3</v>
       </c>
-      <c r="X3" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA3" s="44" t="str">
+      <c r="X3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA3" s="40" t="str">
         <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="49">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="55">
         <v>4</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>132</v>
+      </c>
+      <c r="E4" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="60" t="s">
         <v>140</v>
       </c>
-      <c r="C4" s="51" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E4" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="51" t="s">
-        <v>144</v>
-      </c>
-      <c r="G4" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="53" t="str">
+      <c r="G4" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="45" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M4" s="53" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M4" s="45" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N4" s="53" t="str">
+      <c r="N4" s="45" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O4" s="53" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O4" s="45" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Mobiliário</v>
       </c>
-      <c r="P4" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="Q4" s="44" t="s">
-        <v>152</v>
-      </c>
-      <c r="R4" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="55" t="str">
+      <c r="P4" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q4" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="R4" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T4" s="55" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T4" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U4" s="55" t="str">
+      <c r="U4" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V4" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W4" s="60" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V4" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W4" s="47" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-4</v>
       </c>
-      <c r="X4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y4" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA4" s="44" t="str">
+      <c r="X4" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y4" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="40" t="str">
         <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="49">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="55">
         <v>5</v>
       </c>
-      <c r="B5" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="51" t="s">
+      <c r="B5" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D5" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="D5" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F5" s="51" t="s">
-        <v>146</v>
-      </c>
-      <c r="G5" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L5" s="53" t="str">
+      <c r="E5" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="F5" s="60" t="s">
+        <v>142</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="45" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M5" s="53" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M5" s="45" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N5" s="53" t="str">
+      <c r="N5" s="45" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O5" s="53" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O5" s="45" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Equipamento</v>
       </c>
-      <c r="P5" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q5" s="44" t="s">
-        <v>153</v>
-      </c>
-      <c r="R5" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="55" t="str">
+      <c r="P5" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q5" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="R5" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T5" s="55" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T5" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U5" s="55" t="str">
+      <c r="U5" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V5" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W5" s="60" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V5" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W5" s="47" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-5</v>
       </c>
-      <c r="X5" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y5" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z5" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA5" s="44" t="str">
+      <c r="X5" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA5" s="40" t="str">
         <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="49">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="55">
         <v>6</v>
       </c>
-      <c r="B6" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="51" t="s">
+      <c r="B6" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="50" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" s="50" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="G6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="53" t="str">
+      <c r="E6" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="F6" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="G6" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="45" t="str">
         <f t="shared" si="0"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="M6" s="53" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="M6" s="45" t="str">
         <f t="shared" si="0"/>
         <v>Informação</v>
       </c>
-      <c r="N6" s="53" t="str">
+      <c r="N6" s="45" t="str">
         <f t="shared" si="1"/>
-        <v>Requerida</v>
-      </c>
-      <c r="O6" s="53" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="O6" s="45" t="str">
         <f t="shared" si="1"/>
         <v>Requisito Sistemas</v>
       </c>
-      <c r="P6" s="44" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q6" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="R6" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S6" s="55" t="str">
+      <c r="P6" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="Q6" s="40" t="s">
+        <v>171</v>
+      </c>
+      <c r="R6" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S6" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Contêiner</v>
-      </c>
-      <c r="T6" s="55" t="str">
+        <v>Gestão</v>
+      </c>
+      <c r="T6" s="40" t="str">
         <f t="shared" si="2"/>
         <v>Informação</v>
       </c>
-      <c r="U6" s="55" t="str">
+      <c r="U6" s="40" t="str">
         <f t="shared" si="2"/>
-        <v>Requerida</v>
-      </c>
-      <c r="V6" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W6" s="60" t="str">
+        <v>Contêineres</v>
+      </c>
+      <c r="V6" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W6" s="47" t="str">
         <f t="shared" si="3"/>
         <v>Key-UAS-6</v>
       </c>
-      <c r="X6" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y6" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z6" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA6" s="44" t="str">
+      <c r="X6" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y6" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="40" t="str">
         <f t="shared" si="4"/>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="49">
+    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="55">
         <v>7</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="18" t="s">
+      <c r="B7" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="F7" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="G7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="56" t="str">
+      <c r="E7" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F7" s="61" t="s">
+        <v>86</v>
+      </c>
+      <c r="G7" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="58" t="str">
         <f t="shared" ref="L7:L8" si="5">_xlfn.CONCAT(SUBSTITUTE(C7,"1.",""))</f>
         <v>Operação</v>
       </c>
-      <c r="M7" s="56" t="str">
+      <c r="M7" s="58" t="str">
         <f t="shared" ref="M7:O12" si="6">_xlfn.CONCAT(SUBSTITUTE(D7,"."," "))</f>
         <v>Manutenção</v>
       </c>
-      <c r="N7" s="56" t="str">
+      <c r="N7" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O7" s="56" t="str">
+      <c r="O7" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Drone</v>
       </c>
-      <c r="P7" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="Q7" s="44" t="str">
+      <c r="P7" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q7" s="40" t="str">
         <f t="shared" ref="Q7:Q13" si="7">_xlfn.TRANSLATE(P7,"pt","es")</f>
         <v>Es una aeronave tipo dron o UAS.</v>
       </c>
-      <c r="R7" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="55" t="str">
+      <c r="R7" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="40" t="str">
         <f t="shared" ref="S7:S13" si="8">SUBSTITUTE(C7, ".", " ")</f>
         <v>Operação</v>
       </c>
-      <c r="T7" s="55" t="str">
+      <c r="T7" s="40" t="str">
         <f t="shared" ref="T7:T13" si="9">SUBSTITUTE(D7, ".", " ")</f>
         <v>Manutenção</v>
       </c>
-      <c r="U7" s="55" t="str">
+      <c r="U7" s="40" t="str">
         <f t="shared" ref="U7:U13" si="10">SUBSTITUTE(E7, ".", " ")</f>
         <v>Vistoria</v>
       </c>
-      <c r="V7" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W7" s="60" t="str">
-        <f t="shared" ref="W7:W13" si="11">CONCATENATE("Key-UAS-",A7)</f>
+      <c r="V7" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W7" s="47" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-7</v>
       </c>
-      <c r="X7" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y7" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z7" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA7" s="44" t="str">
+      <c r="X7" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y7" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA7" s="40" t="str">
         <f>_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>It is a drone-type aircraft or UAS.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="49">
+    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="55">
         <v>8</v>
       </c>
-      <c r="B8" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="18" t="s">
+      <c r="B8" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="D8" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="56" t="str">
+      <c r="E8" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" s="61" t="s">
+        <v>99</v>
+      </c>
+      <c r="G8" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="58" t="str">
         <f t="shared" si="5"/>
         <v>Operação</v>
       </c>
-      <c r="M8" s="56" t="str">
+      <c r="M8" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Manutenção</v>
       </c>
-      <c r="N8" s="56" t="str">
+      <c r="N8" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O8" s="56" t="str">
+      <c r="O8" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Voo Plano</v>
       </c>
-      <c r="P8" s="56" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q8" s="44" t="str">
+      <c r="P8" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q8" s="40" t="str">
         <f t="shared" si="7"/>
         <v>Plan de vuelo autónomo.</v>
       </c>
-      <c r="R8" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="55" t="str">
+      <c r="R8" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Operação</v>
       </c>
-      <c r="T8" s="55" t="str">
+      <c r="T8" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Manutenção</v>
       </c>
-      <c r="U8" s="55" t="str">
+      <c r="U8" s="40" t="str">
         <f t="shared" si="10"/>
         <v>Vistoria</v>
       </c>
-      <c r="V8" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W8" s="60" t="str">
-        <f t="shared" si="11"/>
+      <c r="V8" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W8" s="47" t="str">
+        <f t="shared" si="3"/>
         <v>Key-UAS-8</v>
       </c>
-      <c r="X8" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y8" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z8" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA8" s="44" t="str">
-        <f t="shared" ref="AA8:AA13" si="12">_xlfn.TRANSLATE(P8,"pt","en")</f>
+      <c r="X8" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y8" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="40" t="str">
+        <f t="shared" ref="AA8:AA13" si="11">_xlfn.TRANSLATE(P8,"pt","en")</f>
         <v>Autonomous flight plan.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="49">
-        <v>9</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="18" t="s">
+    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="55">
+        <v>9</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I9" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J9" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="56" t="str">
-        <f t="shared" ref="L9" si="13">_xlfn.CONCAT(SUBSTITUTE(C9,"1.",""))</f>
+      <c r="G9" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="58" t="str">
+        <f t="shared" ref="L9" si="12">_xlfn.CONCAT(SUBSTITUTE(C9,"1.",""))</f>
         <v>Operação</v>
       </c>
-      <c r="M9" s="56" t="str">
+      <c r="M9" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Manutenção</v>
       </c>
-      <c r="N9" s="56" t="str">
+      <c r="N9" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O9" s="56" t="str">
+      <c r="O9" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Voo Autônomo</v>
       </c>
-      <c r="P9" s="56" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q9" s="44" t="str">
+      <c r="P9" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q9" s="40" t="str">
         <f t="shared" si="7"/>
         <v>Vuelo autónomo realizado con un dron.</v>
       </c>
-      <c r="R9" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="55" t="str">
+      <c r="R9" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Operação</v>
       </c>
-      <c r="T9" s="55" t="str">
+      <c r="T9" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Manutenção</v>
       </c>
-      <c r="U9" s="55" t="str">
+      <c r="U9" s="40" t="str">
         <f t="shared" si="10"/>
         <v>Vistoria</v>
       </c>
-      <c r="V9" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W9" s="60" t="str">
+      <c r="V9" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W9" s="47" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-9</v>
+      </c>
+      <c r="X9" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y9" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA9" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Key-UAS-9</v>
-      </c>
-      <c r="X9" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y9" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z9" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA9" s="44" t="str">
-        <f t="shared" si="12"/>
         <v>Autonomous flight carried out with a drone.</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="49">
+    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="55">
         <v>10</v>
       </c>
-      <c r="B10" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="18" t="s">
+      <c r="B10" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="D10" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="F10" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="G10" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I10" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J10" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="56" t="str">
-        <f t="shared" ref="L10:L11" si="14">_xlfn.CONCAT(SUBSTITUTE(C10,"1.",""))</f>
+      <c r="E10" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="58" t="str">
+        <f t="shared" ref="L10:L11" si="13">_xlfn.CONCAT(SUBSTITUTE(C10,"1.",""))</f>
         <v>Operação</v>
       </c>
-      <c r="M10" s="56" t="str">
+      <c r="M10" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Manutenção</v>
       </c>
-      <c r="N10" s="56" t="str">
+      <c r="N10" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O10" s="56" t="str">
+      <c r="O10" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Voo Manual</v>
       </c>
-      <c r="P10" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q10" s="44" t="str">
+      <c r="P10" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q10" s="40" t="str">
         <f t="shared" si="7"/>
         <v>El vuelo manual se realiza con dron.</v>
       </c>
-      <c r="R10" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="55" t="str">
+      <c r="R10" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Operação</v>
       </c>
-      <c r="T10" s="55" t="str">
+      <c r="T10" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Manutenção</v>
       </c>
-      <c r="U10" s="55" t="str">
+      <c r="U10" s="40" t="str">
         <f t="shared" si="10"/>
         <v>Vistoria</v>
       </c>
-      <c r="V10" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W10" s="60" t="str">
+      <c r="V10" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W10" s="47" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-10</v>
+      </c>
+      <c r="X10" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y10" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Key-UAS-10</v>
-      </c>
-      <c r="X10" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y10" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z10" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA10" s="44" t="str">
-        <f t="shared" si="12"/>
         <v>Manual flight carried out with drone.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="49">
+    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="55">
         <v>11</v>
       </c>
-      <c r="B11" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="18" t="s">
+      <c r="B11" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="D11" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="G11" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="56" t="str">
-        <f t="shared" si="14"/>
+      <c r="E11" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="61" t="s">
+        <v>84</v>
+      </c>
+      <c r="G11" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I11" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="58" t="str">
+        <f t="shared" si="13"/>
         <v>Operação</v>
       </c>
-      <c r="M11" s="56" t="str">
+      <c r="M11" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Manutenção</v>
       </c>
-      <c r="N11" s="56" t="str">
+      <c r="N11" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O11" s="56" t="str">
+      <c r="O11" s="58" t="str">
         <f t="shared" si="6"/>
         <v>De Campo</v>
       </c>
-      <c r="P11" s="56" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q11" s="44" t="str">
+      <c r="P11" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q11" s="40" t="str">
         <f t="shared" si="7"/>
         <v>Inspección realizada en el terreno.</v>
       </c>
-      <c r="R11" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="55" t="str">
+      <c r="R11" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Operação</v>
       </c>
-      <c r="T11" s="55" t="str">
+      <c r="T11" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Manutenção</v>
       </c>
-      <c r="U11" s="55" t="str">
+      <c r="U11" s="40" t="str">
         <f t="shared" si="10"/>
         <v>Vistoria</v>
       </c>
-      <c r="V11" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W11" s="60" t="str">
+      <c r="V11" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W11" s="47" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-11</v>
+      </c>
+      <c r="X11" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y11" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z11" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Key-UAS-11</v>
-      </c>
-      <c r="X11" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y11" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z11" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA11" s="44" t="str">
-        <f t="shared" si="12"/>
         <v>Inspection carried out in the field.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="49">
+    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="55">
         <v>12</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="18" t="s">
+      <c r="B12" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C12" s="61" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="D12" s="61" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="G12" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J12" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K12" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L12" s="56" t="str">
-        <f t="shared" ref="L12" si="15">_xlfn.CONCAT(SUBSTITUTE(C12,"1.",""))</f>
+      <c r="E12" s="61" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I12" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K12" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="58" t="str">
+        <f t="shared" ref="L12" si="14">_xlfn.CONCAT(SUBSTITUTE(C12,"1.",""))</f>
         <v>Operação</v>
       </c>
-      <c r="M12" s="56" t="str">
+      <c r="M12" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Manutenção</v>
       </c>
-      <c r="N12" s="56" t="str">
+      <c r="N12" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Vistoria</v>
       </c>
-      <c r="O12" s="56" t="str">
+      <c r="O12" s="58" t="str">
         <f t="shared" si="6"/>
         <v>Banco Imagens</v>
       </c>
-      <c r="P12" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q12" s="44" t="str">
+      <c r="P12" s="58" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q12" s="40" t="str">
         <f t="shared" si="7"/>
         <v>Imágenes y vídeos de archivo de los vuelos.</v>
       </c>
-      <c r="R12" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S12" s="55" t="str">
+      <c r="R12" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S12" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Operação</v>
       </c>
-      <c r="T12" s="55" t="str">
+      <c r="T12" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Manutenção</v>
       </c>
-      <c r="U12" s="55" t="str">
+      <c r="U12" s="40" t="str">
         <f t="shared" si="10"/>
         <v>Vistoria</v>
       </c>
-      <c r="V12" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W12" s="60" t="str">
+      <c r="V12" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W12" s="47" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-12</v>
+      </c>
+      <c r="X12" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y12" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA12" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Key-UAS-12</v>
-      </c>
-      <c r="X12" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y12" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z12" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA12" s="44" t="str">
-        <f t="shared" si="12"/>
         <v>Stock images and videos of the flights.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="49">
+    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="55">
         <v>13</v>
       </c>
-      <c r="B13" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="41" t="s">
+      <c r="B13" s="59" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="62" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="62" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="E13" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="F13" s="61" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="K13" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="58" t="str">
+        <f t="shared" ref="L13" si="15">_xlfn.CONCAT(SUBSTITUTE(C13,"1.",""))</f>
+        <v>Temporal</v>
+      </c>
+      <c r="M13" s="58" t="str">
+        <f t="shared" ref="M13" si="16">_xlfn.CONCAT(SUBSTITUTE(D13,"."," "))</f>
+        <v>Evento</v>
+      </c>
+      <c r="N13" s="58" t="str">
+        <f t="shared" ref="N13" si="17">_xlfn.CONCAT(SUBSTITUTE(E13,"."," "))</f>
+        <v>Calendário</v>
+      </c>
+      <c r="O13" s="58" t="str">
+        <f t="shared" ref="O13" si="18">_xlfn.CONCAT(SUBSTITUTE(F13,"."," "))</f>
+        <v>Data</v>
+      </c>
+      <c r="P13" s="58" t="s">
         <v>118</v>
       </c>
-      <c r="F13" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="J13" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K13" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="L13" s="56" t="str">
-        <f t="shared" ref="L13" si="16">_xlfn.CONCAT(SUBSTITUTE(C13,"1.",""))</f>
-        <v>Temporal</v>
-      </c>
-      <c r="M13" s="56" t="str">
-        <f t="shared" ref="M13" si="17">_xlfn.CONCAT(SUBSTITUTE(D13,"."," "))</f>
-        <v>Evento</v>
-      </c>
-      <c r="N13" s="56" t="str">
-        <f t="shared" ref="N13" si="18">_xlfn.CONCAT(SUBSTITUTE(E13,"."," "))</f>
-        <v>Calendário</v>
-      </c>
-      <c r="O13" s="56" t="str">
-        <f t="shared" ref="O13" si="19">_xlfn.CONCAT(SUBSTITUTE(F13,"."," "))</f>
-        <v>Data</v>
-      </c>
-      <c r="P13" s="56" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q13" s="44" t="str">
+      <c r="Q13" s="40" t="str">
         <f t="shared" si="7"/>
         <v>Fecha del evento de inspección.</v>
       </c>
-      <c r="R13" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S13" s="55" t="str">
+      <c r="R13" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="S13" s="40" t="str">
         <f t="shared" si="8"/>
         <v>Temporal</v>
       </c>
-      <c r="T13" s="55" t="str">
+      <c r="T13" s="40" t="str">
         <f t="shared" si="9"/>
         <v>Evento</v>
       </c>
-      <c r="U13" s="55" t="str">
+      <c r="U13" s="40" t="str">
         <f t="shared" si="10"/>
         <v>Calendário</v>
       </c>
-      <c r="V13" s="56" t="s">
-        <v>120</v>
-      </c>
-      <c r="W13" s="60" t="str">
+      <c r="V13" s="58" t="s">
+        <v>119</v>
+      </c>
+      <c r="W13" s="47" t="str">
+        <f t="shared" si="3"/>
+        <v>Key-UAS-13</v>
+      </c>
+      <c r="X13" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y13" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z13" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA13" s="40" t="str">
         <f t="shared" si="11"/>
-        <v>Key-UAS-13</v>
-      </c>
-      <c r="X13" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y13" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z13" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="AA13" s="44" t="str">
-        <f t="shared" si="12"/>
         <v>Date of the inspection event.</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A13">
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="59" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F10 F1">
+    <cfRule type="duplicateValues" dxfId="54" priority="171"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F14:F1048576 F1 F7:F10">
+    <cfRule type="duplicateValues" dxfId="53" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G1:O1">
+    <cfRule type="cellIs" dxfId="52" priority="24" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="34" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="29" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F10 F1">
-    <cfRule type="duplicateValues" dxfId="25" priority="165"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14:F1048576 F1 F7:F10">
-    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G1:O1">
-    <cfRule type="cellIs" dxfId="23" priority="18" operator="equal">
+  <conditionalFormatting sqref="AA1 AA7:AA13">
+    <cfRule type="cellIs" dxfId="51" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA13">
-    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B13">
+    <cfRule type="cellIs" dxfId="50" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="49" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="45" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3303,14 +3504,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779E4F22-2568-4D5A-A538-DD63A5C43724}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="5.69140625" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="5.7109375" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.69140625" style="11" customWidth="1"/>
-    <col min="2" max="10" width="5.69140625" style="12"/>
-    <col min="11" max="16384" width="5.69140625" style="23"/>
+    <col min="1" max="1" width="2.7109375" style="11" customWidth="1"/>
+    <col min="2" max="10" width="5.7109375" style="12"/>
+    <col min="11" max="16384" width="5.7109375" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.15">
       <c r="A1" s="21">
         <v>1</v>
       </c>
@@ -3375,7 +3576,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="7.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="8.25" x14ac:dyDescent="0.15">
       <c r="A2" s="21">
         <v>2</v>
       </c>
@@ -3449,16 +3650,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4328B84A-AA24-421E-9F4E-92D6A71CA3BE}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.84375" style="13" customWidth="1"/>
-    <col min="3" max="3" width="7.69140625" style="13" customWidth="1"/>
-    <col min="4" max="4" width="7.3828125" style="13" customWidth="1"/>
-    <col min="5" max="16384" width="9.15234375" style="13"/>
+    <col min="2" max="2" width="7.85546875" style="13" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" style="13" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" style="13" customWidth="1"/>
+    <col min="5" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -3466,23 +3667,23 @@
         <v>14</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>2</v>
       </c>
-      <c r="B2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="31" t="s">
+      <c r="B2" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="29" t="s">
         <v>9</v>
       </c>
     </row>
@@ -3495,38 +3696,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D50BAA-DAEA-47D5-8FAA-A68A87918655}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AA62"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.15234375" customWidth="1"/>
-    <col min="4" max="4" width="6.3046875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.765625" customWidth="1"/>
-    <col min="6" max="6" width="6.3046875" customWidth="1"/>
-    <col min="7" max="7" width="4.23046875" customWidth="1"/>
-    <col min="8" max="8" width="6.23046875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.4609375" customWidth="1"/>
-    <col min="10" max="10" width="2.69140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="3.07421875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.3046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="25.23046875" customWidth="1"/>
-    <col min="18" max="18" width="4.84375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27.53515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.3828125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.84375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.69140625" style="66" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.3828125" style="66" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="3.84375" style="66" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.15234375" style="66" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="5.3046875" style="66"/>
-    <col min="27" max="27" width="5.921875" style="66" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="34" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" style="53" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.85546875" style="53" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.7109375" style="53" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.5703125" style="53" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.28515625" style="53" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="8" style="53" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:27" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -3536,28 +3736,28 @@
       <c r="C1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="32" t="s">
+      <c r="D1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="E1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="32" t="s">
+      <c r="G1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="I1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="32" t="s">
+      <c r="J1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="30" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="15" t="s">
@@ -3572,16 +3772,16 @@
       <c r="O1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="32" t="s">
+      <c r="P1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="32" t="s">
+      <c r="Q1" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="32" t="s">
+      <c r="R1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="32" t="s">
+      <c r="S1" s="30" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="15" t="s">
@@ -3590,1022 +3790,1022 @@
       <c r="U1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="62" t="s">
+      <c r="V1" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="W1" s="63" t="s">
-        <v>170</v>
-      </c>
-      <c r="X1" s="64" t="s">
+      <c r="W1" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="X1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Y1" s="63" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z1" s="64" t="s">
+      <c r="Y1" s="50" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z1" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="AA1" s="63" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AA1" s="50" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16">
         <v>2</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="M2" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="N2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="M2" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="N2" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O2" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="P2" s="33" t="s">
         <v>16</v>
       </c>
       <c r="Q2" s="20" t="s">
-        <v>159</v>
-      </c>
-      <c r="R2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="R2" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="52" t="s">
         <v>9</v>
       </c>
       <c r="W2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="37" t="s">
+      <c r="X2" s="35" t="s">
         <v>9</v>
       </c>
       <c r="Y2" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="35" t="s">
         <v>9</v>
       </c>
       <c r="AA2" s="20" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="16">
         <v>3</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K3" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="M3" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="J3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O3" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="P3" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="R3" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U3" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="N3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="O3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P3" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q3" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="R3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T3" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" s="65" t="s">
-        <v>9</v>
-      </c>
       <c r="W3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X3" s="37" t="s">
-        <v>9</v>
+        <v>166</v>
+      </c>
+      <c r="X3" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="Y3" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="37" t="s">
-        <v>9</v>
+        <v>166</v>
+      </c>
+      <c r="Z3" s="35" t="s">
+        <v>164</v>
       </c>
       <c r="AA3" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="16">
         <v>4</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K4" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L4" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="M4" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="J4" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K4" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N4" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q4" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="R4" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S4" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U4" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="V4" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="W4" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="X4" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="N4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="O4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q4" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="R4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T4" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V4" s="65" t="s">
-        <v>9</v>
-      </c>
-      <c r="W4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="X4" s="37" t="s">
-        <v>9</v>
-      </c>
       <c r="Y4" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z4" s="37" t="s">
-        <v>9</v>
+        <v>166</v>
+      </c>
+      <c r="Z4" s="35" t="s">
+        <v>164</v>
       </c>
       <c r="AA4" s="20" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16">
         <v>5</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="J5" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K5" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="32" t="s">
         <v>9</v>
       </c>
       <c r="L5" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M5" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N5" s="35" t="s">
-        <v>91</v>
+        <v>110</v>
+      </c>
+      <c r="M5" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="N5" s="33" t="s">
+        <v>9</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="P5" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="P5" s="33" t="s">
         <v>16</v>
       </c>
       <c r="Q5" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="R5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T5" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="U5" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="V5" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="W5" s="67" t="s">
-        <v>176</v>
-      </c>
-      <c r="X5" s="37" t="s">
-        <v>172</v>
+        <v>111</v>
+      </c>
+      <c r="R5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T5" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="U5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V5" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="W5" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="X5" s="35" t="s">
+        <v>9</v>
       </c>
       <c r="Y5" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="Z5" s="37" t="s">
-        <v>173</v>
+        <v>9</v>
+      </c>
+      <c r="Z5" s="35" t="s">
+        <v>9</v>
       </c>
       <c r="AA5" s="20" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="16">
         <v>6</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="J6" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="32" t="s">
         <v>9</v>
       </c>
       <c r="L6" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M6" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="M6" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="N6" s="33" t="s">
         <v>9</v>
       </c>
       <c r="O6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P6" s="35" t="s">
+      <c r="P6" s="33" t="s">
         <v>16</v>
       </c>
       <c r="Q6" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="R6" s="35" t="s">
+        <v>111</v>
+      </c>
+      <c r="R6" s="33" t="s">
         <v>9</v>
       </c>
       <c r="S6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T6" s="35" t="s">
+      <c r="T6" s="33" t="s">
         <v>9</v>
       </c>
       <c r="U6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="V6" s="65" t="s">
-        <v>171</v>
+      <c r="V6" s="52" t="s">
+        <v>9</v>
       </c>
       <c r="W6" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X6" s="37" t="s">
-        <v>172</v>
+        <v>9</v>
+      </c>
+      <c r="X6" s="35" t="s">
+        <v>9</v>
       </c>
       <c r="Y6" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z6" s="37" t="s">
-        <v>173</v>
+        <v>9</v>
+      </c>
+      <c r="Z6" s="35" t="s">
+        <v>9</v>
       </c>
       <c r="AA6" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16">
         <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="O7" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="P7" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q7" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="R7" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S7" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="T7" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="U7" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="V7" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="W7" s="54" t="s">
+        <v>167</v>
+      </c>
+      <c r="X7" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y7" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="Z7" s="35" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA7" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="C7" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="J7" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K7" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M7" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P7" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q7" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="R7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="S7" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="T7" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U7" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V7" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="W7" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X7" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y7" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z7" s="37" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA7" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>8</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>98</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="I8" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="J8" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L8" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="33" t="s">
         <v>9</v>
       </c>
       <c r="M8" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P8" s="35" t="s">
+      <c r="N8" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="O8" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" s="33" t="s">
         <v>16</v>
       </c>
       <c r="Q8" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="R8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="S8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T8" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="U8" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="V8" s="65" t="s">
-        <v>171</v>
+        <v>159</v>
+      </c>
+      <c r="R8" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T8" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="U8" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V8" s="52" t="s">
+        <v>162</v>
       </c>
       <c r="W8" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X8" s="37" t="s">
-        <v>172</v>
+        <v>166</v>
+      </c>
+      <c r="X8" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="Y8" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z8" s="37" t="s">
-        <v>173</v>
+        <v>166</v>
+      </c>
+      <c r="Z8" s="35" t="s">
+        <v>164</v>
       </c>
       <c r="AA8" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="16">
         <v>9</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>141</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>98</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="J9" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="F9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K9" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="33" t="s">
         <v>9</v>
       </c>
       <c r="M9" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="O9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="P9" s="35" t="s">
+      <c r="N9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P9" s="33" t="s">
         <v>16</v>
       </c>
       <c r="Q9" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="R9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="S9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T9" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="U9" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="V9" s="65" t="s">
-        <v>171</v>
+        <v>159</v>
+      </c>
+      <c r="R9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="S9" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="T9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="U9" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V9" s="52" t="s">
+        <v>162</v>
       </c>
       <c r="W9" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X9" s="37" t="s">
-        <v>172</v>
+        <v>166</v>
+      </c>
+      <c r="X9" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="Y9" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z9" s="37" t="s">
-        <v>173</v>
+        <v>166</v>
+      </c>
+      <c r="Z9" s="35" t="s">
+        <v>164</v>
       </c>
       <c r="AA9" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16">
         <v>10</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>121</v>
+        <v>94</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="31" t="s">
+        <v>120</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="J10" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K10" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="33" t="s">
         <v>9</v>
       </c>
       <c r="M10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="35" t="s">
+      <c r="N10" s="33" t="s">
         <v>9</v>
       </c>
       <c r="O10" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P10" s="35" t="s">
+      <c r="P10" s="33" t="s">
         <v>16</v>
       </c>
       <c r="Q10" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="R10" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T10" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="U10" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="V10" s="65" t="s">
-        <v>171</v>
+        <v>148</v>
+      </c>
+      <c r="R10" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="U10" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="V10" s="52" t="s">
+        <v>162</v>
       </c>
       <c r="W10" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X10" s="37" t="s">
-        <v>172</v>
+        <v>166</v>
+      </c>
+      <c r="X10" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="Y10" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z10" s="37" t="s">
-        <v>173</v>
+        <v>166</v>
+      </c>
+      <c r="Z10" s="35" t="s">
+        <v>164</v>
       </c>
       <c r="AA10" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="16">
         <v>11</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>121</v>
+        <v>94</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="31" t="s">
+        <v>120</v>
       </c>
       <c r="I11" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="J11" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="34" t="s">
-        <v>9</v>
-      </c>
-      <c r="L11" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="K11" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="33" t="s">
         <v>9</v>
       </c>
       <c r="M11" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="35" t="s">
+      <c r="N11" s="33" t="s">
         <v>9</v>
       </c>
       <c r="O11" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="P11" s="35" t="s">
+      <c r="P11" s="33" t="s">
         <v>16</v>
       </c>
       <c r="Q11" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="R11" s="37" t="s">
-        <v>9</v>
-      </c>
-      <c r="S11" s="38" t="s">
-        <v>9</v>
-      </c>
-      <c r="T11" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="U11" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="V11" s="65" t="s">
-        <v>171</v>
+        <v>148</v>
+      </c>
+      <c r="R11" s="35" t="s">
+        <v>9</v>
+      </c>
+      <c r="S11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="U11" s="37" t="s">
+        <v>147</v>
+      </c>
+      <c r="V11" s="52" t="s">
+        <v>162</v>
       </c>
       <c r="W11" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X11" s="37" t="s">
-        <v>172</v>
+        <v>166</v>
+      </c>
+      <c r="X11" s="35" t="s">
+        <v>163</v>
       </c>
       <c r="Y11" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z11" s="37" t="s">
-        <v>173</v>
+        <v>166</v>
+      </c>
+      <c r="Z11" s="35" t="s">
+        <v>164</v>
       </c>
       <c r="AA11" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16">
         <v>12</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F12" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="H12" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J12" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="L12" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="O12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P12" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="R12" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="S12" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="T12" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="U12" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V12" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="W12" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="G12" s="19" t="s">
+      <c r="X12" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="Y12" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z12" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="H12" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="I12" s="34" t="s">
-        <v>108</v>
-      </c>
-      <c r="J12" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="K12" s="34" t="s">
-        <v>96</v>
-      </c>
-      <c r="L12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="O12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P12" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q12" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="S12" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="T12" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U12" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V12" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="W12" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X12" s="37" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y12" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z12" s="37" t="s">
-        <v>173</v>
-      </c>
       <c r="AA12" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="16">
         <v>13</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="O13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="P13" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="R13" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="S13" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="T13" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="U13" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="V13" s="52" t="s">
+        <v>162</v>
+      </c>
+      <c r="W13" s="20" t="s">
         <v>166</v>
       </c>
-      <c r="E13" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="G13" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="34" t="s">
-        <v>107</v>
-      </c>
-      <c r="J13" s="33" t="s">
-        <v>97</v>
-      </c>
-      <c r="K13" s="34" t="s">
-        <v>103</v>
-      </c>
-      <c r="L13" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="M13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="N13" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="O13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="P13" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q13" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="S13" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="T13" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="U13" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="V13" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="W13" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="X13" s="65" t="s">
-        <v>172</v>
+      <c r="X13" s="52" t="s">
+        <v>163</v>
       </c>
       <c r="Y13" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="Z13" s="37" t="s">
-        <v>173</v>
+        <v>166</v>
+      </c>
+      <c r="Z13" s="35" t="s">
+        <v>164</v>
       </c>
       <c r="AA13" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V14"/>
       <c r="W14"/>
       <c r="X14"/>
@@ -4613,7 +4813,7 @@
       <c r="Z14"/>
       <c r="AA14"/>
     </row>
-    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V15"/>
       <c r="W15"/>
       <c r="X15"/>
@@ -4621,7 +4821,7 @@
       <c r="Z15"/>
       <c r="AA15"/>
     </row>
-    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="V16"/>
       <c r="W16"/>
       <c r="X16"/>
@@ -4629,105 +4829,56 @@
       <c r="Z16"/>
       <c r="AA16"/>
     </row>
-    <row r="17" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="18" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="19" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="20" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="21" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="22" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="23" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="24" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="25" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="26" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="28" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="31" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="37" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="42" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="49" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="56" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="17" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="B1:B13">
-    <cfRule type="duplicateValues" dxfId="21" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="230"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="178"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E9">
-    <cfRule type="duplicateValues" dxfId="18" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G12">
-    <cfRule type="duplicateValues" dxfId="15" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G13">
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I8">
-    <cfRule type="duplicateValues" dxfId="9" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I9">
-    <cfRule type="duplicateValues" dxfId="6" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="V63:AA1048576 V1:AA4 V5 X5 Z5:AA5 X7:X12 V7:W13 V6:AA6 Y7:AA13">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X13">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="W5">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Y5">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Versão5/VANT/Ontologia_DRONE.xlsx
+++ b/Versão5/VANT/Ontologia_DRONE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\VANT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5637961D-E3AA-4210-8C46-BEC3287D4E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D62BD2-5299-4C30-8AB2-FB5DFBD03639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="527" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="31" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="218">
   <si>
     <t>Edição</t>
   </si>
@@ -439,15 +439,6 @@
     <t>Projeto</t>
   </si>
   <si>
-    <t>Patologias</t>
-  </si>
-  <si>
-    <t>Diagnósticos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voo de drone planejado dentro das ações de diagnóstico preventivo de patologias. </t>
-  </si>
-  <si>
     <t>[ 2Q.18.18 ]</t>
   </si>
   <si>
@@ -463,18 +454,6 @@
     <t>Vistorias</t>
   </si>
   <si>
-    <t>Voo.Diagnóstico</t>
-  </si>
-  <si>
-    <t>Voo.Levantamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voo de drone planejado dentro das ações de diagnóstico preventivo de patologias para levantamento de dados. </t>
-  </si>
-  <si>
-    <t>É uma aeronave tipo drone ou UAS com dispositivo LIDAR incorporado.</t>
-  </si>
-  <si>
     <t>É uma aeronave tipo drone ou UAS padrão.</t>
   </si>
   <si>
@@ -704,6 +683,48 @@
   </si>
   <si>
     <t>"[ 5I.80.90.10.16 ]"</t>
+  </si>
+  <si>
+    <t>Video gravado durante um voo.</t>
+  </si>
+  <si>
+    <t>É uma aeronave tipo drone ou UAS com dispositivo LIDAR (Light Detection and Ranging) incorporado.</t>
+  </si>
+  <si>
+    <t>Vídeo.Voo</t>
+  </si>
+  <si>
+    <t>Preventiva</t>
+  </si>
+  <si>
+    <t>Corretiva</t>
+  </si>
+  <si>
+    <t>Preditiva</t>
+  </si>
+  <si>
+    <t>Voo.Preditivo</t>
+  </si>
+  <si>
+    <t>Voo.Corretivo</t>
+  </si>
+  <si>
+    <t>Voo.Preventivo</t>
+  </si>
+  <si>
+    <t>Diagnóstica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voo de drone planejado para tomar ações corretivas de patologias. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Voo de drone planejado para tomar ações de conservação dos sistemas prediais. </t>
+  </si>
+  <si>
+    <t>"[ 5I.80.90.26.12 ]"</t>
+  </si>
+  <si>
+    <t>Voo de drone planejado para prever futuras manutenções ou patologias.</t>
   </si>
 </sst>
 </file>
@@ -1170,6 +1191,14 @@
   <dxfs count="15">
     <dxf>
       <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1177,14 +1206,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1835,7 +1856,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46224.363032291665</v>
+        <v>46224.421018518522</v>
       </c>
       <c r="C18" s="27" t="s">
         <v>102</v>
@@ -1917,16 +1938,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348BB721-29D9-4DD8-81B8-03CCB3CE3CCF}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.140625" style="32" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="32" customWidth="1"/>
-    <col min="4" max="4" width="6" style="32" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" style="32" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="32" customWidth="1"/>
-    <col min="7" max="11" width="7" style="32" customWidth="1"/>
+    <col min="2" max="2" width="4.42578125" style="32" customWidth="1"/>
+    <col min="3" max="3" width="6.85546875" style="32" customWidth="1"/>
+    <col min="4" max="4" width="5.42578125" style="32" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" style="32" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="32" customWidth="1"/>
+    <col min="7" max="11" width="6.5703125" style="32" customWidth="1"/>
     <col min="12" max="12" width="6.7109375" style="32" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.28515625" style="32" customWidth="1"/>
     <col min="14" max="14" width="6.140625" style="32" customWidth="1"/>
@@ -2029,7 +2050,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="36">
         <v>2</v>
       </c>
@@ -2104,7 +2125,7 @@
         <v>94</v>
       </c>
       <c r="W2" s="31" t="str">
-        <f t="shared" ref="W2:W17" si="3">CONCATENATE("Key-UAS-",A2)</f>
+        <f t="shared" ref="W2:W16" si="3">CONCATENATE("Key-UAS-",A2)</f>
         <v>Key-UAS-2</v>
       </c>
       <c r="X2" s="24" t="s">
@@ -2121,7 +2142,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
         <v>3</v>
       </c>
@@ -2213,7 +2234,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
         <v>4</v>
       </c>
@@ -2305,7 +2326,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
         <v>5</v>
       </c>
@@ -2397,7 +2418,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>6</v>
       </c>
@@ -2489,7 +2510,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
         <v>7</v>
       </c>
@@ -2582,7 +2603,7 @@
         <v>Date of the inspection event.</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>8</v>
       </c>
@@ -2596,7 +2617,7 @@
         <v>75</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F8" s="41" t="s">
         <v>81</v>
@@ -2633,7 +2654,7 @@
         <v>Drone</v>
       </c>
       <c r="P8" s="35" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="Q8" s="24" t="str">
         <f t="shared" ref="Q8" si="16">_xlfn.TRANSLATE(P8,"pt","es")</f>
@@ -2662,20 +2683,20 @@
         <v>Key-UAS-8</v>
       </c>
       <c r="X8" s="24" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Y8" s="24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Z8" s="24" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AA8" s="24" t="str">
         <f>_xlfn.TRANSLATE(P8,"pt","en")</f>
         <v>It is a standard drone-type aircraft or UAS.</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="36">
         <v>9</v>
       </c>
@@ -2689,10 +2710,10 @@
         <v>75</v>
       </c>
       <c r="E9" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F9" s="41" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G9" s="33" t="s">
         <v>9</v>
@@ -2714,7 +2735,7 @@
         <v>Operação</v>
       </c>
       <c r="M9" s="35" t="str">
-        <f t="shared" ref="M9:O14" si="18">_xlfn.CONCAT(SUBSTITUTE(D9,"."," "))</f>
+        <f t="shared" ref="M9:O15" si="18">_xlfn.CONCAT(SUBSTITUTE(D9,"."," "))</f>
         <v>Manutenção</v>
       </c>
       <c r="N9" s="35" t="str">
@@ -2726,25 +2747,25 @@
         <v>Drone LIDAR</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>133</v>
+        <v>205</v>
       </c>
       <c r="Q9" s="24" t="str">
-        <f t="shared" ref="Q9:Q14" si="19">_xlfn.TRANSLATE(P9,"pt","es")</f>
-        <v>Es una aeronave tipo dron o UAS con dispositivo LIDAR incorporado.</v>
+        <f t="shared" ref="Q9:Q15" si="19">_xlfn.TRANSLATE(P9,"pt","es")</f>
+        <v>Es una aeronave tipo dron o UAS con un dispositivo LIDAR (Detección y Alcance de Luz) incorporado.</v>
       </c>
       <c r="R9" s="24" t="s">
         <v>9</v>
       </c>
       <c r="S9" s="24" t="str">
-        <f t="shared" ref="S9:S14" si="20">SUBSTITUTE(C9, ".", " ")</f>
+        <f t="shared" ref="S9:S15" si="20">SUBSTITUTE(C9, ".", " ")</f>
         <v>Operação</v>
       </c>
       <c r="T9" s="24" t="str">
-        <f t="shared" ref="T9:T14" si="21">SUBSTITUTE(D9, ".", " ")</f>
+        <f t="shared" ref="T9:T15" si="21">SUBSTITUTE(D9, ".", " ")</f>
         <v>Manutenção</v>
       </c>
       <c r="U9" s="24" t="str">
-        <f t="shared" ref="U9:U14" si="22">SUBSTITUTE(E9, ".", " ")</f>
+        <f t="shared" ref="U9:U15" si="22">SUBSTITUTE(E9, ".", " ")</f>
         <v>Vistorias</v>
       </c>
       <c r="V9" s="35" t="s">
@@ -2755,20 +2776,20 @@
         <v>Key-UAS-9</v>
       </c>
       <c r="X9" s="24" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="Y9" s="24" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="Z9" s="24" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AA9" s="24" t="str">
         <f>_xlfn.TRANSLATE(P9,"pt","en")</f>
-        <v>It is a drone-type aircraft or UAS with built-in LIDAR device.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>It is a drone-type aircraft or UAS with a built-in LIDAR (Light Detection and Ranging) device.</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>10</v>
       </c>
@@ -2782,7 +2803,7 @@
         <v>75</v>
       </c>
       <c r="E10" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F10" s="41" t="s">
         <v>85</v>
@@ -2857,11 +2878,11 @@
         <v>9</v>
       </c>
       <c r="AA10" s="24" t="str">
-        <f t="shared" ref="AA10:AA14" si="23">_xlfn.TRANSLATE(P10,"pt","en")</f>
+        <f t="shared" ref="AA10:AA15" si="23">_xlfn.TRANSLATE(P10,"pt","en")</f>
         <v>Autonomous flight plan.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <v>11</v>
       </c>
@@ -2875,7 +2896,7 @@
         <v>75</v>
       </c>
       <c r="E11" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F11" s="41" t="s">
         <v>77</v>
@@ -2954,7 +2975,7 @@
         <v>Autonomous flight carried out with a drone.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>12</v>
       </c>
@@ -2968,7 +2989,7 @@
         <v>75</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F12" s="41" t="s">
         <v>78</v>
@@ -2989,7 +3010,7 @@
         <v>9</v>
       </c>
       <c r="L12" s="35" t="str">
-        <f t="shared" ref="L12:L15" si="25">_xlfn.CONCAT(SUBSTITUTE(C12,"1.",""))</f>
+        <f t="shared" ref="L12:L16" si="25">_xlfn.CONCAT(SUBSTITUTE(C12,"1.",""))</f>
         <v>Operação</v>
       </c>
       <c r="M12" s="35" t="str">
@@ -3047,7 +3068,7 @@
         <v>Manual flight carried out with drone.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
         <v>13</v>
       </c>
@@ -3061,7 +3082,7 @@
         <v>75</v>
       </c>
       <c r="E13" s="41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F13" s="41" t="s">
         <v>79</v>
@@ -3140,7 +3161,7 @@
         <v>Inspection carried out in the field.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>14</v>
       </c>
@@ -3154,10 +3175,10 @@
         <v>75</v>
       </c>
       <c r="E14" s="41" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F14" s="41" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="G14" s="33" t="s">
         <v>9</v>
@@ -3175,7 +3196,7 @@
         <v>9</v>
       </c>
       <c r="L14" s="35" t="str">
-        <f t="shared" ref="L14" si="26">_xlfn.CONCAT(SUBSTITUTE(C14,"1.",""))</f>
+        <f t="shared" ref="L14:L15" si="26">_xlfn.CONCAT(SUBSTITUTE(C14,"1.",""))</f>
         <v>Operação</v>
       </c>
       <c r="M14" s="35" t="str">
@@ -3191,7 +3212,7 @@
         <v>Imagem Banco</v>
       </c>
       <c r="P14" s="35" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="Q14" s="24" t="str">
         <f t="shared" si="19"/>
@@ -3226,14 +3247,14 @@
         <v>9</v>
       </c>
       <c r="Z14" s="24" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="AA14" s="24" t="str">
         <f t="shared" si="23"/>
         <v>Photographic Image Bank corresponding to a Maintenance Flight performed.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>15</v>
       </c>
@@ -3247,10 +3268,10 @@
         <v>75</v>
       </c>
       <c r="E15" s="41" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="F15" s="41" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="G15" s="33" t="s">
         <v>9</v>
@@ -3268,135 +3289,135 @@
         <v>9</v>
       </c>
       <c r="L15" s="35" t="str">
+        <f t="shared" si="26"/>
+        <v>Operação</v>
+      </c>
+      <c r="M15" s="35" t="str">
+        <f t="shared" si="18"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="N15" s="35" t="str">
+        <f t="shared" si="18"/>
+        <v>Imagens</v>
+      </c>
+      <c r="O15" s="35" t="str">
+        <f t="shared" si="18"/>
+        <v>Imagem WayPoint</v>
+      </c>
+      <c r="P15" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q15" s="24" t="str">
+        <f t="shared" si="19"/>
+        <v>Imagen fotográfica correspondiente a un WayPoint.</v>
+      </c>
+      <c r="R15" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="S15" s="24" t="str">
+        <f t="shared" si="20"/>
+        <v>Operação</v>
+      </c>
+      <c r="T15" s="24" t="str">
+        <f t="shared" si="21"/>
+        <v>Manutenção</v>
+      </c>
+      <c r="U15" s="24" t="str">
+        <f t="shared" si="22"/>
+        <v>Imagens</v>
+      </c>
+      <c r="V15" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="W15" s="31" t="str">
+        <f t="shared" ref="W15" si="27">CONCATENATE("Key-UAS-",A15)</f>
+        <v>Key-UAS-15</v>
+      </c>
+      <c r="X15" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y15" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA15" s="24" t="str">
+        <f t="shared" si="23"/>
+        <v>Photographic image corresponding to a WayPoint.</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="36">
+        <v>16</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="F16" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="35" t="str">
         <f t="shared" si="25"/>
         <v>Operação</v>
       </c>
-      <c r="M15" s="35" t="str">
-        <f t="shared" ref="M15" si="27">_xlfn.CONCAT(SUBSTITUTE(D15,"."," "))</f>
+      <c r="M16" s="35" t="str">
+        <f t="shared" ref="M16" si="28">_xlfn.CONCAT(SUBSTITUTE(D16,"."," "))</f>
         <v>Manutenção</v>
       </c>
-      <c r="N15" s="35" t="str">
-        <f t="shared" ref="N15" si="28">_xlfn.CONCAT(SUBSTITUTE(E15,"."," "))</f>
+      <c r="N16" s="35" t="str">
+        <f t="shared" ref="N16" si="29">_xlfn.CONCAT(SUBSTITUTE(E16,"."," "))</f>
         <v>Imagens</v>
       </c>
-      <c r="O15" s="35" t="str">
-        <f t="shared" ref="O15" si="29">_xlfn.CONCAT(SUBSTITUTE(F15,"."," "))</f>
-        <v>Imagem WayPoint</v>
-      </c>
-      <c r="P15" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q15" s="24" t="str">
-        <f t="shared" ref="Q15" si="30">_xlfn.TRANSLATE(P15,"pt","es")</f>
-        <v>Imagen fotográfica correspondiente a un WayPoint.</v>
-      </c>
-      <c r="R15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S15" s="24" t="str">
-        <f t="shared" ref="S15" si="31">SUBSTITUTE(C15, ".", " ")</f>
+      <c r="O16" s="35" t="str">
+        <f t="shared" ref="O16" si="30">_xlfn.CONCAT(SUBSTITUTE(F16,"."," "))</f>
+        <v>Vídeo Voo</v>
+      </c>
+      <c r="P16" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q16" s="24" t="str">
+        <f t="shared" ref="Q16" si="31">_xlfn.TRANSLATE(P16,"pt","es")</f>
+        <v>Vídeo grabado durante un vuelo.</v>
+      </c>
+      <c r="R16" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="S16" s="24" t="str">
+        <f t="shared" ref="S16" si="32">SUBSTITUTE(C16, ".", " ")</f>
         <v>Operação</v>
       </c>
-      <c r="T15" s="24" t="str">
-        <f t="shared" ref="T15" si="32">SUBSTITUTE(D15, ".", " ")</f>
+      <c r="T16" s="24" t="str">
+        <f t="shared" ref="T16" si="33">SUBSTITUTE(D16, ".", " ")</f>
         <v>Manutenção</v>
       </c>
-      <c r="U15" s="24" t="str">
-        <f t="shared" ref="U15" si="33">SUBSTITUTE(E15, ".", " ")</f>
+      <c r="U16" s="24" t="str">
+        <f t="shared" ref="U16" si="34">SUBSTITUTE(E16, ".", " ")</f>
         <v>Imagens</v>
-      </c>
-      <c r="V15" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="W15" s="31" t="str">
-        <f t="shared" si="3"/>
-        <v>Key-UAS-15</v>
-      </c>
-      <c r="X15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y15" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z15" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA15" s="24" t="str">
-        <f t="shared" ref="AA15" si="34">_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Photographic image corresponding to a WayPoint.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="36">
-        <v>16</v>
-      </c>
-      <c r="B16" s="38" t="s">
-        <v>121</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="41" t="s">
-        <v>130</v>
-      </c>
-      <c r="G16" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="I16" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="J16" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="K16" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="L16" s="35" t="str">
-        <f t="shared" ref="L16" si="35">_xlfn.CONCAT(SUBSTITUTE(C16,"1.",""))</f>
-        <v>De.Manutenção</v>
-      </c>
-      <c r="M16" s="35" t="str">
-        <f t="shared" ref="M16" si="36">_xlfn.CONCAT(SUBSTITUTE(D16,"."," "))</f>
-        <v>Diagnósticos</v>
-      </c>
-      <c r="N16" s="35" t="str">
-        <f t="shared" ref="N16" si="37">_xlfn.CONCAT(SUBSTITUTE(E16,"."," "))</f>
-        <v>Patologias</v>
-      </c>
-      <c r="O16" s="35" t="str">
-        <f t="shared" ref="O16" si="38">_xlfn.CONCAT(SUBSTITUTE(F16,"."," "))</f>
-        <v>Voo Diagnóstico</v>
-      </c>
-      <c r="P16" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q16" s="24" t="str">
-        <f t="shared" ref="Q16" si="39">_xlfn.TRANSLATE(P16,"pt","es")</f>
-        <v>El vuelo con dron está planificado dentro del diagnóstico preventivo de patologías.</v>
-      </c>
-      <c r="R16" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="S16" s="24" t="str">
-        <f t="shared" ref="S16" si="40">SUBSTITUTE(C16, ".", " ")</f>
-        <v>De Manutenção</v>
-      </c>
-      <c r="T16" s="24" t="str">
-        <f t="shared" ref="T16" si="41">SUBSTITUTE(D16, ".", " ")</f>
-        <v>Diagnósticos</v>
-      </c>
-      <c r="U16" s="24" t="str">
-        <f t="shared" ref="U16" si="42">SUBSTITUTE(E16, ".", " ")</f>
-        <v>Patologias</v>
       </c>
       <c r="V16" s="35" t="s">
         <v>94</v>
@@ -3412,14 +3433,14 @@
         <v>9</v>
       </c>
       <c r="Z16" s="24" t="s">
-        <v>9</v>
+        <v>202</v>
       </c>
       <c r="AA16" s="24" t="str">
-        <f t="shared" ref="AA16" si="43">_xlfn.TRANSLATE(P16,"pt","en")</f>
-        <v>Drone flight planned within the preventive diagnosis of pathologies.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" ref="AA16" si="35">_xlfn.TRANSLATE(P16,"pt","en")</f>
+        <v>Video recorded during a flight.</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>17</v>
       </c>
@@ -3427,16 +3448,16 @@
         <v>121</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="D17" s="40" t="s">
-        <v>123</v>
+        <v>213</v>
       </c>
       <c r="E17" s="40" t="s">
-        <v>122</v>
+        <v>207</v>
       </c>
       <c r="F17" s="41" t="s">
-        <v>131</v>
+        <v>212</v>
       </c>
       <c r="G17" s="33" t="s">
         <v>9</v>
@@ -3454,48 +3475,48 @@
         <v>9</v>
       </c>
       <c r="L17" s="35" t="str">
-        <f t="shared" ref="L17" si="44">_xlfn.CONCAT(SUBSTITUTE(C17,"1.",""))</f>
+        <f t="shared" ref="L17:L19" si="36">_xlfn.CONCAT(SUBSTITUTE(C17,"1.",""))</f>
         <v>De.Manutenção</v>
       </c>
       <c r="M17" s="35" t="str">
-        <f t="shared" ref="M17" si="45">_xlfn.CONCAT(SUBSTITUTE(D17,"."," "))</f>
-        <v>Diagnósticos</v>
+        <f t="shared" ref="M17:M19" si="37">_xlfn.CONCAT(SUBSTITUTE(D17,"."," "))</f>
+        <v>Diagnóstica</v>
       </c>
       <c r="N17" s="35" t="str">
-        <f t="shared" ref="N17" si="46">_xlfn.CONCAT(SUBSTITUTE(E17,"."," "))</f>
-        <v>Patologias</v>
+        <f t="shared" ref="N17:N19" si="38">_xlfn.CONCAT(SUBSTITUTE(E17,"."," "))</f>
+        <v>Preventiva</v>
       </c>
       <c r="O17" s="35" t="str">
-        <f t="shared" ref="O17" si="47">_xlfn.CONCAT(SUBSTITUTE(F17,"."," "))</f>
-        <v>Voo Levantamento</v>
+        <f t="shared" ref="O17:O19" si="39">_xlfn.CONCAT(SUBSTITUTE(F17,"."," "))</f>
+        <v>Voo Preventivo</v>
       </c>
       <c r="P17" s="35" t="s">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="Q17" s="24" t="str">
-        <f t="shared" ref="Q17" si="48">_xlfn.TRANSLATE(P17,"pt","es")</f>
-        <v>El vuelo con dron está planificado dentro del diagnóstico preventivo de patologías para la recogida de datos.</v>
+        <f t="shared" ref="Q17:Q19" si="40">_xlfn.TRANSLATE(P17,"pt","es")</f>
+        <v>El vuelo con drones planeó realizar acciones de conservación de los sistemas del edificio.</v>
       </c>
       <c r="R17" s="24" t="s">
         <v>9</v>
       </c>
       <c r="S17" s="24" t="str">
-        <f t="shared" ref="S17" si="49">SUBSTITUTE(C17, ".", " ")</f>
+        <f t="shared" ref="S17:S19" si="41">SUBSTITUTE(C17, ".", " ")</f>
         <v>De Manutenção</v>
       </c>
       <c r="T17" s="24" t="str">
-        <f t="shared" ref="T17" si="50">SUBSTITUTE(D17, ".", " ")</f>
-        <v>Diagnósticos</v>
+        <f t="shared" ref="T17:T19" si="42">SUBSTITUTE(D17, ".", " ")</f>
+        <v>Diagnóstica</v>
       </c>
       <c r="U17" s="24" t="str">
-        <f t="shared" ref="U17" si="51">SUBSTITUTE(E17, ".", " ")</f>
-        <v>Patologias</v>
+        <f t="shared" ref="U17:U19" si="43">SUBSTITUTE(E17, ".", " ")</f>
+        <v>Preventiva</v>
       </c>
       <c r="V17" s="35" t="s">
         <v>94</v>
       </c>
       <c r="W17" s="31" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="W17:W19" si="44">CONCATENATE("Key-UAS-",A17)</f>
         <v>Key-UAS-17</v>
       </c>
       <c r="X17" s="24" t="s">
@@ -3508,8 +3529,194 @@
         <v>9</v>
       </c>
       <c r="AA17" s="24" t="str">
-        <f t="shared" ref="AA17" si="52">_xlfn.TRANSLATE(P17,"pt","en")</f>
-        <v>Drone flight planned within the preventive diagnosis of pathologies for data collection.</v>
+        <f t="shared" ref="AA17:AA19" si="45">_xlfn.TRANSLATE(P17,"pt","en")</f>
+        <v>Drone flight planned to take conservation actions of building systems.</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="36">
+        <v>18</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>208</v>
+      </c>
+      <c r="F18" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="35" t="str">
+        <f t="shared" si="36"/>
+        <v>De.Manutenção</v>
+      </c>
+      <c r="M18" s="35" t="str">
+        <f t="shared" si="37"/>
+        <v>Diagnóstica</v>
+      </c>
+      <c r="N18" s="35" t="str">
+        <f t="shared" si="38"/>
+        <v>Corretiva</v>
+      </c>
+      <c r="O18" s="35" t="str">
+        <f t="shared" si="39"/>
+        <v>Voo Corretivo</v>
+      </c>
+      <c r="P18" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q18" s="24" t="str">
+        <f t="shared" si="40"/>
+        <v>El vuelo de drones planeó tomar medidas correctivas para patologías.</v>
+      </c>
+      <c r="R18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="S18" s="24" t="str">
+        <f t="shared" si="41"/>
+        <v>De Manutenção</v>
+      </c>
+      <c r="T18" s="24" t="str">
+        <f t="shared" si="42"/>
+        <v>Diagnóstica</v>
+      </c>
+      <c r="U18" s="24" t="str">
+        <f t="shared" si="43"/>
+        <v>Corretiva</v>
+      </c>
+      <c r="V18" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="W18" s="31" t="str">
+        <f t="shared" si="44"/>
+        <v>Key-UAS-18</v>
+      </c>
+      <c r="X18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z18" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="24" t="str">
+        <f t="shared" si="45"/>
+        <v>Drone flight planned to take corrective actions for pathologies.</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="36">
+        <v>19</v>
+      </c>
+      <c r="B19" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="40" t="s">
+        <v>213</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" s="41" t="s">
+        <v>210</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="K19" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="35" t="str">
+        <f t="shared" si="36"/>
+        <v>De.Manutenção</v>
+      </c>
+      <c r="M19" s="35" t="str">
+        <f t="shared" si="37"/>
+        <v>Diagnóstica</v>
+      </c>
+      <c r="N19" s="35" t="str">
+        <f t="shared" si="38"/>
+        <v>Preditiva</v>
+      </c>
+      <c r="O19" s="35" t="str">
+        <f t="shared" si="39"/>
+        <v>Voo Preditivo</v>
+      </c>
+      <c r="P19" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q19" s="24" t="str">
+        <f t="shared" si="40"/>
+        <v>Vuelo planificado con dron para predecir el mantenimiento futuro o patologías.</v>
+      </c>
+      <c r="R19" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="S19" s="24" t="str">
+        <f t="shared" si="41"/>
+        <v>De Manutenção</v>
+      </c>
+      <c r="T19" s="24" t="str">
+        <f t="shared" si="42"/>
+        <v>Diagnóstica</v>
+      </c>
+      <c r="U19" s="24" t="str">
+        <f t="shared" si="43"/>
+        <v>Preditiva</v>
+      </c>
+      <c r="V19" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="W19" s="31" t="str">
+        <f t="shared" si="44"/>
+        <v>Key-UAS-19</v>
+      </c>
+      <c r="X19" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y19" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z19" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA19" s="24" t="str">
+        <f t="shared" si="45"/>
+        <v>Planned drone flight to predict future maintenance or pathologies.</v>
       </c>
     </row>
   </sheetData>
@@ -3532,7 +3739,7 @@
     <cfRule type="duplicateValues" dxfId="5" priority="3"/>
     <cfRule type="duplicateValues" dxfId="4" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F18:F1048576 F1 F8:F12">
+  <conditionalFormatting sqref="F17:F1048576 F1 F8:F12">
     <cfRule type="duplicateValues" dxfId="3" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G1:O1">
@@ -3540,8 +3747,8 @@
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA17 A2:B17">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA1:AA19 A2:B19">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3711,7 +3918,7 @@
     <col min="5" max="16384" width="9.140625" style="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="6.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:4" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="8">
         <v>1</v>
       </c>
@@ -3750,114 +3957,115 @@
   <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.85546875" customWidth="1"/>
-    <col min="3" max="3" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.140625" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="6.85546875" customWidth="1"/>
-    <col min="7" max="7" width="4.28515625" customWidth="1"/>
+    <col min="7" max="7" width="4.85546875" customWidth="1"/>
     <col min="8" max="8" width="7.140625" customWidth="1"/>
     <col min="9" max="9" width="7.28515625" customWidth="1"/>
-    <col min="10" max="10" width="3" customWidth="1"/>
-    <col min="11" max="11" width="3.42578125" customWidth="1"/>
-    <col min="12" max="12" width="2.42578125" customWidth="1"/>
+    <col min="10" max="10" width="3.7109375" customWidth="1"/>
+    <col min="11" max="11" width="4" customWidth="1"/>
+    <col min="12" max="12" width="3.140625" customWidth="1"/>
     <col min="13" max="13" width="14.5703125" customWidth="1"/>
     <col min="14" max="14" width="4.5703125" customWidth="1"/>
     <col min="15" max="15" width="7.140625" customWidth="1"/>
-    <col min="16" max="16" width="5" customWidth="1"/>
-    <col min="17" max="17" width="27.42578125" customWidth="1"/>
-    <col min="18" max="18" width="5.7109375" customWidth="1"/>
-    <col min="19" max="19" width="29.7109375" customWidth="1"/>
+    <col min="16" max="16" width="5.42578125" customWidth="1"/>
+    <col min="17" max="17" width="28.85546875" customWidth="1"/>
+    <col min="18" max="18" width="6.42578125" customWidth="1"/>
+    <col min="19" max="19" width="31.85546875" customWidth="1"/>
     <col min="20" max="20" width="2.85546875" customWidth="1"/>
-    <col min="21" max="22" width="6.28515625" customWidth="1"/>
-    <col min="23" max="23" width="8.85546875" customWidth="1"/>
-    <col min="24" max="24" width="4.7109375" customWidth="1"/>
-    <col min="25" max="25" width="6.42578125" customWidth="1"/>
-    <col min="26" max="26" width="5.5703125" customWidth="1"/>
-    <col min="27" max="27" width="9.28515625" customWidth="1"/>
+    <col min="21" max="21" width="7.28515625" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" customWidth="1"/>
+    <col min="24" max="24" width="4.85546875" customWidth="1"/>
+    <col min="25" max="25" width="7.42578125" customWidth="1"/>
+    <col min="26" max="26" width="6.28515625" customWidth="1"/>
+    <col min="27" max="27" width="10.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C1" s="43" t="s">
         <v>13</v>
       </c>
       <c r="D1" s="44" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E1" s="43" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="44" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G1" s="44" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="45" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="I1" s="43" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="44" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="K1" s="44" t="s">
         <v>2</v>
       </c>
       <c r="L1" s="43" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="M1" s="43" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="43" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="O1" s="43" t="s">
         <v>2</v>
       </c>
       <c r="P1" s="44" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="Q1" s="44" t="s">
         <v>2</v>
       </c>
       <c r="R1" s="44" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="S1" s="44" t="s">
         <v>2</v>
       </c>
       <c r="T1" s="43" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="U1" s="43" t="s">
         <v>2</v>
       </c>
       <c r="V1" s="46" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="W1" s="47" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="X1" s="48" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="Y1" s="47" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="Z1" s="48" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="AA1" s="47" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3865,7 +4073,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>81</v>
@@ -3901,46 +4109,46 @@
         <v>9</v>
       </c>
       <c r="N2" s="57" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="O2" s="58" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="P2" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q2" s="58" t="s">
+        <v>153</v>
+      </c>
+      <c r="R2" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="T2" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="V2" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="W2" s="61" t="s">
+        <v>154</v>
+      </c>
+      <c r="X2" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="Q2" s="58" t="s">
-        <v>160</v>
-      </c>
-      <c r="R2" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S2" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="T2" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="U2" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="V2" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="W2" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="X2" s="54" t="s">
-        <v>149</v>
-      </c>
       <c r="Y2" s="58" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="Z2" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA2" s="58" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -3948,7 +4156,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C3" s="51" t="s">
         <v>105</v>
@@ -3978,10 +4186,10 @@
         <v>9</v>
       </c>
       <c r="L3" s="54" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M3" s="55" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="N3" s="54" t="s">
         <v>9</v>
@@ -3990,40 +4198,40 @@
         <v>9</v>
       </c>
       <c r="P3" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q3" s="58" t="s">
+        <v>136</v>
+      </c>
+      <c r="R3" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="S3" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="U3" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="V3" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="W3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="X3" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y3" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z3" s="54" t="s">
         <v>143</v>
       </c>
-      <c r="R3" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="S3" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="T3" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="U3" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="V3" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="W3" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="X3" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y3" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z3" s="54" t="s">
-        <v>150</v>
-      </c>
       <c r="AA3" s="58" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4031,16 +4239,16 @@
         <v>4</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="C4" s="51" t="s">
         <v>105</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E4" s="60" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="F4" s="52" t="s">
         <v>9</v>
@@ -4049,10 +4257,10 @@
         <v>9</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I4" s="60" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J4" s="52" t="s">
         <v>9</v>
@@ -4073,10 +4281,10 @@
         <v>9</v>
       </c>
       <c r="P4" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q4" s="58" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="R4" s="54" t="s">
         <v>9</v>
@@ -4103,10 +4311,10 @@
         <v>9</v>
       </c>
       <c r="Z4" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA4" s="58" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4114,17 +4322,17 @@
         <v>5</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="C5" s="51" t="s">
         <v>105</v>
       </c>
       <c r="D5" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="60" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="60" t="s">
-        <v>151</v>
-      </c>
       <c r="F5" s="52" t="s">
         <v>9</v>
       </c>
@@ -4132,10 +4340,10 @@
         <v>9</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I5" s="60" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J5" s="52" t="s">
         <v>9</v>
@@ -4156,10 +4364,10 @@
         <v>9</v>
       </c>
       <c r="P5" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q5" s="58" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="R5" s="54" t="s">
         <v>9</v>
@@ -4186,10 +4394,10 @@
         <v>9</v>
       </c>
       <c r="Z5" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA5" s="58" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4197,10 +4405,10 @@
         <v>6</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="C6" s="51" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D6" s="52" t="s">
         <v>9</v>
@@ -4215,23 +4423,23 @@
         <v>9</v>
       </c>
       <c r="H6" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="I6" s="60" t="s">
+        <v>173</v>
+      </c>
+      <c r="J6" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K6" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="M6" s="55" t="s">
         <v>146</v>
       </c>
-      <c r="I6" s="60" t="s">
-        <v>180</v>
-      </c>
-      <c r="J6" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K6" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="M6" s="55" t="s">
-        <v>153</v>
-      </c>
       <c r="N6" s="57" t="s">
         <v>9</v>
       </c>
@@ -4239,10 +4447,10 @@
         <v>9</v>
       </c>
       <c r="P6" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q6" s="58" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="R6" s="57" t="s">
         <v>9</v>
@@ -4269,10 +4477,10 @@
         <v>9</v>
       </c>
       <c r="Z6" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA6" s="58" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4280,10 +4488,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C7" s="51" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D7" s="52" t="s">
         <v>9</v>
@@ -4298,10 +4506,10 @@
         <v>9</v>
       </c>
       <c r="H7" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I7" s="60" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="J7" s="52" t="s">
         <v>9</v>
@@ -4310,10 +4518,10 @@
         <v>9</v>
       </c>
       <c r="L7" s="54" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M7" s="55" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="N7" s="57" t="s">
         <v>9</v>
@@ -4322,10 +4530,10 @@
         <v>9</v>
       </c>
       <c r="P7" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q7" s="58" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="R7" s="57" t="s">
         <v>9</v>
@@ -4352,10 +4560,10 @@
         <v>9</v>
       </c>
       <c r="Z7" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA7" s="58" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4363,10 +4571,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C8" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D8" s="52" t="s">
         <v>9</v>
@@ -4381,10 +4589,10 @@
         <v>9</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I8" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J8" s="52" t="s">
         <v>9</v>
@@ -4405,10 +4613,10 @@
         <v>9</v>
       </c>
       <c r="P8" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q8" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R8" s="57" t="s">
         <v>9</v>
@@ -4435,10 +4643,10 @@
         <v>9</v>
       </c>
       <c r="Z8" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA8" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4446,10 +4654,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C9" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D9" s="52" t="s">
         <v>9</v>
@@ -4464,10 +4672,10 @@
         <v>9</v>
       </c>
       <c r="H9" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I9" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J9" s="52" t="s">
         <v>9</v>
@@ -4488,10 +4696,10 @@
         <v>9</v>
       </c>
       <c r="P9" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q9" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R9" s="57" t="s">
         <v>9</v>
@@ -4518,10 +4726,10 @@
         <v>9</v>
       </c>
       <c r="Z9" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA9" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4529,10 +4737,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="C10" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D10" s="52" t="s">
         <v>9</v>
@@ -4547,10 +4755,10 @@
         <v>9</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I10" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J10" s="52" t="s">
         <v>9</v>
@@ -4571,10 +4779,10 @@
         <v>9</v>
       </c>
       <c r="P10" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q10" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R10" s="57" t="s">
         <v>9</v>
@@ -4601,10 +4809,10 @@
         <v>9</v>
       </c>
       <c r="Z10" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA10" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4612,10 +4820,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="C11" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D11" s="52" t="s">
         <v>9</v>
@@ -4630,10 +4838,10 @@
         <v>9</v>
       </c>
       <c r="H11" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I11" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J11" s="52" t="s">
         <v>9</v>
@@ -4654,10 +4862,10 @@
         <v>9</v>
       </c>
       <c r="P11" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q11" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R11" s="57" t="s">
         <v>9</v>
@@ -4684,10 +4892,10 @@
         <v>9</v>
       </c>
       <c r="Z11" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA11" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4695,10 +4903,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="C12" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D12" s="52" t="s">
         <v>9</v>
@@ -4713,10 +4921,10 @@
         <v>9</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I12" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J12" s="52" t="s">
         <v>9</v>
@@ -4737,10 +4945,10 @@
         <v>9</v>
       </c>
       <c r="P12" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q12" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R12" s="57" t="s">
         <v>9</v>
@@ -4767,10 +4975,10 @@
         <v>9</v>
       </c>
       <c r="Z12" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA12" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4778,10 +4986,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="50" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C13" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D13" s="52" t="s">
         <v>9</v>
@@ -4796,10 +5004,10 @@
         <v>9</v>
       </c>
       <c r="H13" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I13" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J13" s="52" t="s">
         <v>9</v>
@@ -4820,10 +5028,10 @@
         <v>9</v>
       </c>
       <c r="P13" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q13" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R13" s="57" t="s">
         <v>9</v>
@@ -4850,10 +5058,10 @@
         <v>9</v>
       </c>
       <c r="Z13" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA13" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4861,10 +5069,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="50" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="C14" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D14" s="52" t="s">
         <v>9</v>
@@ -4879,10 +5087,10 @@
         <v>9</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I14" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J14" s="52" t="s">
         <v>9</v>
@@ -4903,10 +5111,10 @@
         <v>9</v>
       </c>
       <c r="P14" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q14" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R14" s="57" t="s">
         <v>9</v>
@@ -4933,10 +5141,10 @@
         <v>9</v>
       </c>
       <c r="Z14" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA14" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4944,10 +5152,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="50" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C15" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D15" s="52" t="s">
         <v>9</v>
@@ -4962,10 +5170,10 @@
         <v>9</v>
       </c>
       <c r="H15" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I15" s="60" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J15" s="52" t="s">
         <v>9</v>
@@ -4986,10 +5194,10 @@
         <v>9</v>
       </c>
       <c r="P15" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q15" s="58" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="R15" s="57" t="s">
         <v>9</v>
@@ -5016,10 +5224,10 @@
         <v>9</v>
       </c>
       <c r="Z15" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA15" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5027,10 +5235,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="50" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="C16" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D16" s="52" t="s">
         <v>9</v>
@@ -5045,10 +5253,10 @@
         <v>9</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I16" s="60" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J16" s="52" t="s">
         <v>9</v>
@@ -5069,10 +5277,10 @@
         <v>9</v>
       </c>
       <c r="P16" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q16" s="58" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="R16" s="57" t="s">
         <v>9</v>
@@ -5099,10 +5307,10 @@
         <v>9</v>
       </c>
       <c r="Z16" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA16" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5110,53 +5318,53 @@
         <v>17</v>
       </c>
       <c r="B17" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="I17" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="J17" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K17" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="M17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="N17" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="O17" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="P17" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q17" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="C17" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="D17" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="I17" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="J17" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K17" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="L17" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="M17" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="N17" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="O17" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="P17" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q17" s="58" t="s">
-        <v>204</v>
-      </c>
       <c r="R17" s="57" t="s">
         <v>9</v>
       </c>
@@ -5182,10 +5390,10 @@
         <v>9</v>
       </c>
       <c r="Z17" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA17" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5193,10 +5401,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="50" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D18" s="52" t="s">
         <v>9</v>
@@ -5211,10 +5419,10 @@
         <v>9</v>
       </c>
       <c r="H18" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I18" s="60" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J18" s="52" t="s">
         <v>9</v>
@@ -5235,10 +5443,10 @@
         <v>9</v>
       </c>
       <c r="P18" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q18" s="58" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="R18" s="57" t="s">
         <v>9</v>
@@ -5265,10 +5473,10 @@
         <v>9</v>
       </c>
       <c r="Z18" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA18" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5276,10 +5484,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="50" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D19" s="52" t="s">
         <v>9</v>
@@ -5294,10 +5502,10 @@
         <v>9</v>
       </c>
       <c r="H19" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I19" s="60" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J19" s="52" t="s">
         <v>9</v>
@@ -5318,10 +5526,10 @@
         <v>9</v>
       </c>
       <c r="P19" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q19" s="58" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="R19" s="57" t="s">
         <v>9</v>
@@ -5348,10 +5556,10 @@
         <v>9</v>
       </c>
       <c r="Z19" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA19" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5359,10 +5567,10 @@
         <v>20</v>
       </c>
       <c r="B20" s="50" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D20" s="52" t="s">
         <v>9</v>
@@ -5377,10 +5585,10 @@
         <v>9</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I20" s="60" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J20" s="52" t="s">
         <v>9</v>
@@ -5401,10 +5609,10 @@
         <v>9</v>
       </c>
       <c r="P20" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q20" s="58" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="R20" s="57" t="s">
         <v>9</v>
@@ -5431,10 +5639,10 @@
         <v>9</v>
       </c>
       <c r="Z20" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA20" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5442,10 +5650,10 @@
         <v>21</v>
       </c>
       <c r="B21" s="50" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D21" s="52" t="s">
         <v>9</v>
@@ -5460,10 +5668,10 @@
         <v>9</v>
       </c>
       <c r="H21" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I21" s="60" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J21" s="52" t="s">
         <v>9</v>
@@ -5484,10 +5692,10 @@
         <v>9</v>
       </c>
       <c r="P21" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q21" s="58" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="R21" s="57" t="s">
         <v>9</v>
@@ -5514,10 +5722,10 @@
         <v>9</v>
       </c>
       <c r="Z21" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA21" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5525,10 +5733,10 @@
         <v>22</v>
       </c>
       <c r="B22" s="50" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="C22" s="51" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="D22" s="52" t="s">
         <v>9</v>
@@ -5543,10 +5751,10 @@
         <v>9</v>
       </c>
       <c r="H22" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I22" s="60" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J22" s="52" t="s">
         <v>9</v>
@@ -5567,10 +5775,10 @@
         <v>9</v>
       </c>
       <c r="P22" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q22" s="58" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="R22" s="57" t="s">
         <v>9</v>
@@ -5597,10 +5805,10 @@
         <v>9</v>
       </c>
       <c r="Z22" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA22" s="58" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5608,82 +5816,82 @@
         <v>23</v>
       </c>
       <c r="B23" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="G23" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="J23" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="K23" s="53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="M23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="O23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="P23" s="57" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q23" s="58" t="s">
+        <v>197</v>
+      </c>
+      <c r="R23" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="S23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="T23" s="57" t="s">
+        <v>9</v>
+      </c>
+      <c r="U23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="V23" s="59" t="s">
+        <v>9</v>
+      </c>
+      <c r="W23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="X23" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y23" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z23" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="AA23" s="58" t="s">
         <v>203</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>185</v>
-      </c>
-      <c r="D23" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="52" t="s">
-        <v>146</v>
-      </c>
-      <c r="I23" s="60" t="s">
-        <v>155</v>
-      </c>
-      <c r="J23" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="K23" s="53" t="s">
-        <v>9</v>
-      </c>
-      <c r="L23" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="M23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="N23" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="O23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="P23" s="57" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q23" s="58" t="s">
-        <v>204</v>
-      </c>
-      <c r="R23" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="S23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="T23" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="U23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="V23" s="59" t="s">
-        <v>9</v>
-      </c>
-      <c r="W23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="X23" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y23" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="Z23" s="54" t="s">
-        <v>150</v>
-      </c>
-      <c r="AA23" s="58" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5691,16 +5899,16 @@
         <v>24</v>
       </c>
       <c r="B24" s="50" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C24" s="51" t="s">
         <v>85</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E24" s="60" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F24" s="52" t="s">
         <v>9</v>
@@ -5733,10 +5941,10 @@
         <v>9</v>
       </c>
       <c r="P24" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q24" s="58" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="R24" s="57" t="s">
         <v>9</v>
@@ -5763,10 +5971,10 @@
         <v>9</v>
       </c>
       <c r="Z24" s="54" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="AA24" s="58" t="s">
-        <v>9</v>
+        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5774,16 +5982,16 @@
         <v>25</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C25" s="51" t="s">
         <v>85</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E25" s="60" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F25" s="52" t="s">
         <v>9</v>
@@ -5816,10 +6024,10 @@
         <v>9</v>
       </c>
       <c r="P25" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q25" s="58" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="R25" s="57" t="s">
         <v>9</v>
@@ -5846,10 +6054,10 @@
         <v>9</v>
       </c>
       <c r="Z25" s="54" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="AA25" s="58" t="s">
-        <v>9</v>
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5857,7 +6065,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C26" s="51" t="s">
         <v>84</v>
@@ -5875,10 +6083,10 @@
         <v>9</v>
       </c>
       <c r="H26" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I26" s="60" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J26" s="52" t="s">
         <v>9</v>
@@ -5899,10 +6107,10 @@
         <v>9</v>
       </c>
       <c r="P26" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q26" s="58" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="R26" s="54" t="s">
         <v>9</v>
@@ -5911,10 +6119,10 @@
         <v>9</v>
       </c>
       <c r="T26" s="54" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="U26" s="62" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="V26" s="54" t="s">
         <v>9</v>
@@ -5929,10 +6137,10 @@
         <v>9</v>
       </c>
       <c r="Z26" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA26" s="58" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -5940,7 +6148,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="50" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="C27" s="51" t="s">
         <v>84</v>
@@ -5958,10 +6166,10 @@
         <v>9</v>
       </c>
       <c r="H27" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I27" s="60" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="J27" s="52" t="s">
         <v>9</v>
@@ -5982,10 +6190,10 @@
         <v>9</v>
       </c>
       <c r="P27" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q27" s="58" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="R27" s="54" t="s">
         <v>9</v>
@@ -5994,10 +6202,10 @@
         <v>9</v>
       </c>
       <c r="T27" s="54" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="U27" s="62" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="V27" s="54" t="s">
         <v>9</v>
@@ -6012,10 +6220,10 @@
         <v>9</v>
       </c>
       <c r="Z27" s="54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="AA27" s="58" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -6023,34 +6231,34 @@
         <v>28</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="C28" s="51" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E28" s="60" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="G28" s="60" t="s">
         <v>157</v>
       </c>
-      <c r="F28" s="52" t="s">
-        <v>174</v>
-      </c>
-      <c r="G28" s="60" t="s">
-        <v>164</v>
-      </c>
       <c r="H28" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I28" s="53" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="J28" s="52" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="K28" s="53" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="L28" s="57" t="s">
         <v>9</v>
@@ -6065,16 +6273,16 @@
         <v>9</v>
       </c>
       <c r="P28" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q28" s="58" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="R28" s="57" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="S28" s="58" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="T28" s="57" t="s">
         <v>9</v>
@@ -6106,35 +6314,35 @@
         <v>29</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="C29" s="51" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E29" s="60" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F29" s="52" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="G29" s="60" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="H29" s="52" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="I29" s="53" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="J29" s="52" t="s">
+        <v>137</v>
+      </c>
+      <c r="K29" s="53" t="s">
         <v>144</v>
       </c>
-      <c r="K29" s="53" t="s">
-        <v>151</v>
-      </c>
       <c r="L29" s="57" t="s">
         <v>9</v>
       </c>
@@ -6148,16 +6356,16 @@
         <v>9</v>
       </c>
       <c r="P29" s="57" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="Q29" s="58" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="R29" s="57" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="S29" s="58" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="T29" s="57" t="s">
         <v>9</v>
@@ -6187,7 +6395,7 @@
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
   <conditionalFormatting sqref="B1:B29">
-    <cfRule type="duplicateValues" dxfId="0" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="181"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
